--- a/mainWidget/mainWidget/src/database/计算模型-快速烤燃试验.xlsx
+++ b/mainWidget/mainWidget/src/database/计算模型-快速烤燃试验.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6066285-E140-48C3-A79F-40478702FF8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28F7B325-4BA8-4DEB-9326-5CC66CEEDAE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="1364">
   <si>
     <t>序号</t>
   </si>
@@ -308,1225 +308,4130 @@
   </si>
   <si>
     <t>22.4016</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>331.8477</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>373.3258</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>331.8008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>22.4328</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>488.9082</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>385.8733</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>369.5315</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>385.786</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>488.9728</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>491.3035</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>442.1412</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>426.9798</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>442.1449</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>491.2941</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>486.1875</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>460.713</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>446.8288</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>460.7098</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>486.1558</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>485.908</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>460.5964</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>446.7142</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>460.6042</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>485.8588</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>491.0708</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>441.9908</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>426.8266</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>442.009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>491.0449</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>488.7709</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>385.7218</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>369.3697</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>385.6569</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>488.8337</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>22.4717</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>331.8362</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>373.24</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>331.8161</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>21.8551</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0067</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0138</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0139</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0183</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0174</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.016</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0188</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0168</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.015</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.019</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0141</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1051</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0805</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0054</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0806</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1053</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1029</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0811</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0052</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.081</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.105</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.214</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.4983</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3633</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.4984</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2142</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1625</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.443</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3396</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2138</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.4982</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3632</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1623</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.4424</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3391</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.4425</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1626</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0959</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.402</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3056</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0961</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.096</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.4027</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3063</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0481</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1087</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.109</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0479</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1345</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0602</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0476</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1383</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0527</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0379</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1382</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1413</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0523</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0373</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0372</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1412</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0526</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1381</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1343</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0475</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0601</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1344</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0478</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1086</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1089</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0103</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0512</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0596</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0651</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0693</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0728</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0655</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0724</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0754</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0656</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0715</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0742</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0716</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0743</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0725</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0755</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0652</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0729</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.9756</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.3321</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.4481</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.3318</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.9727</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.7068</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0249</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.024</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.7078</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.6717</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.9906</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.3223</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.9907</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.6719</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.6844</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.1831</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.5467</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.6841</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.5468</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.6817</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.1832</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.6715</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.9899</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.3216</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.6698</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.7065</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0273</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1983</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0265</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.7066</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.9725</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.3326</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.4479</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.3325</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.9701</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0278</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0844</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0958</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0279</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1132</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1268</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1294</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1267</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1123</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1286</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1308</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1091</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.028</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0845</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0959</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0277</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1295</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1124</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1092</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1296</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1315</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0057</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0884</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0984</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0883</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0878</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0135</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0138</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0134</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0879</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0905</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0313</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0939</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.034</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0373</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0055</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0137</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0904</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0938</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0341</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.6292</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.6209</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.6293</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0375</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.9381</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.2831</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.216</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.2827</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.9378</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.9106</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.4744</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.4323</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.9103</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.8634</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.5238</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.4899</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.863</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.5237</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.4897</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.5236</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.8632</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.4741</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.4319</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.9104</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.2826</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.2155</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.2823</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0364</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.6295</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0378</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-5.3473</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.4405</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-5.8514</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.4429</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-5.4008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-9.3345</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-4.4795</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-4.563</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-4.4785</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-9.3385</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-10.0757</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-5.6645</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-5.3448</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-5.6633</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-10.0799</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-10.6672</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-5.8577</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.4491</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-5.3699</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-5.3647</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.4455</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-9.3419</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-4.4858</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-4.5684</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-9.3422</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-10.0806</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-5.3425</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-5.6638</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-10.6711</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-10.0805</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-5.5021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-5.0367</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-5.5022</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-10.671</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-10.6718</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-5.5049</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-5.0417</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-5.5056</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.0405</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.9989</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.0111</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.0404</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.999</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.0113</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.8982</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.776</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.7969</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.7761</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.8983</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.9048</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.6515</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.6581</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.6516</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.9049</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.9205</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.6046</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.6055</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.6047</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.9206</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.9203</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.6041</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.8981</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.7756</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.7963</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.7755</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.9047</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.651</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.6574</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.6048</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>384.1948-0.0141*B+0.0000*C+0.0660*D-0.1014*E-0.0623*F+0.0000*G+1.3396*H-0.0820*I-0.0355*J-0.7972*K-6.1943*L+0.7361*M</t>
+  </si>
+  <si>
+    <t>384.1948</t>
+  </si>
+  <si>
+    <t>-0.0141</t>
+  </si>
+  <si>
+    <t>0.0660</t>
+  </si>
+  <si>
+    <t>-0.1014</t>
+  </si>
+  <si>
+    <t>-0.0623</t>
+  </si>
+  <si>
+    <t>1.3396</t>
+  </si>
+  <si>
+    <t>-0.0820</t>
+  </si>
+  <si>
+    <t>-0.0355</t>
+  </si>
+  <si>
+    <t>-0.7972</t>
+  </si>
+  <si>
+    <t>-6.1943</t>
+  </si>
+  <si>
+    <t>0.7361</t>
+  </si>
+  <si>
+    <t>324.5253-0.0178*B+0.0000*C+0.2193*D-0.0812*E-0.0810*F+0.0000*G+0.1383*H-0.1069*I-0.0340*J-1.0926*K-4.1612*L+0.8154*M</t>
+  </si>
+  <si>
+    <t>324.5253</t>
+  </si>
+  <si>
+    <t>-0.0178</t>
+  </si>
+  <si>
+    <t>0.2193</t>
+  </si>
+  <si>
+    <t>-0.0812</t>
+  </si>
+  <si>
+    <t>-0.0810</t>
+  </si>
+  <si>
+    <t>0.1383</t>
+  </si>
+  <si>
+    <t>-0.1069</t>
+  </si>
+  <si>
+    <t>-0.0340</t>
+  </si>
+  <si>
+    <t>-1.0926</t>
+  </si>
+  <si>
+    <t>-4.1612</t>
+  </si>
+  <si>
+    <t>0.8154</t>
+  </si>
+  <si>
+    <t>376.9493-0.0141*B+0.0000*C+0.2293*D-0.0659*E-0.0603*F+0.0000*G-0.9674*H-0.0856*I-0.0304*J-1.2475*K-8.3455*L+0.8382*M</t>
+  </si>
+  <si>
+    <t>376.9493</t>
+  </si>
+  <si>
+    <t>0.2293</t>
+  </si>
+  <si>
+    <t>-0.0659</t>
+  </si>
+  <si>
+    <t>-0.0603</t>
+  </si>
+  <si>
+    <t>-0.9674</t>
+  </si>
+  <si>
+    <t>-0.0856</t>
+  </si>
+  <si>
+    <t>-0.0304</t>
+  </si>
+  <si>
+    <t>-1.2475</t>
+  </si>
+  <si>
+    <t>-8.3455</t>
+  </si>
+  <si>
+    <t>0.8382</t>
+  </si>
+  <si>
+    <t>313.3209-0.0141*B+0.0000*C+0.2610*D-0.0928*E-0.0684*F+0.0000*G-1.1218*H-0.0967*I+0.0017*J-1.3269*K-3.7846*L+0.7730*M</t>
+  </si>
+  <si>
+    <t>313.3209</t>
+  </si>
+  <si>
+    <t>0.2610</t>
+  </si>
+  <si>
+    <t>-0.0928</t>
+  </si>
+  <si>
+    <t>-0.0684</t>
+  </si>
+  <si>
+    <t>-1.1218</t>
+  </si>
+  <si>
+    <t>-0.0967</t>
+  </si>
+  <si>
+    <t>0.0017</t>
+  </si>
+  <si>
+    <t>-1.3269</t>
+  </si>
+  <si>
+    <t>-3.7846</t>
+  </si>
+  <si>
+    <t>0.7730</t>
+  </si>
+  <si>
+    <t>295.8035-0.0124*B+0.0000*C+0.3675*D-0.0621*E-0.0687*F+0.0000*G+0.1447*H-0.1096*I-0.0770*J-1.1855*K-8.3496*L+0.9168*M</t>
+  </si>
+  <si>
+    <t>295.8035</t>
+  </si>
+  <si>
+    <t>-0.0124</t>
+  </si>
+  <si>
+    <t>0.3675</t>
+  </si>
+  <si>
+    <t>-0.0621</t>
+  </si>
+  <si>
+    <t>-0.0687</t>
+  </si>
+  <si>
+    <t>0.1447</t>
+  </si>
+  <si>
+    <t>-0.1096</t>
+  </si>
+  <si>
+    <t>-0.0770</t>
+  </si>
+  <si>
+    <t>-1.1855</t>
+  </si>
+  <si>
+    <t>-8.3496</t>
+  </si>
+  <si>
+    <t>0.9168</t>
+  </si>
+  <si>
+    <t>486.8771-0.0178*B+0.0000*C+0.2116*D-0.0754*E-0.0741*F+0.0000*G-0.0019*H-0.1260*I-0.0769*J-1.2328*K-7.0422*L+0.7531*M</t>
+  </si>
+  <si>
+    <t>486.8771</t>
+  </si>
+  <si>
+    <t>0.2116</t>
+  </si>
+  <si>
+    <t>-0.0754</t>
+  </si>
+  <si>
+    <t>-0.0741</t>
+  </si>
+  <si>
+    <t>-0.0019</t>
+  </si>
+  <si>
+    <t>-0.1260</t>
+  </si>
+  <si>
+    <t>-0.0769</t>
+  </si>
+  <si>
+    <t>-1.2328</t>
+  </si>
+  <si>
+    <t>-7.0422</t>
+  </si>
+  <si>
+    <t>0.7531</t>
+  </si>
+  <si>
+    <t>489.5038-0.0156*B+0.0000*C+0.0672*D-0.0767*E-0.0770*F+0.0000*G+0.6564*H-0.1296*I-0.0438*J-0.9520*K-7.6390*L+0.7414*M</t>
+  </si>
+  <si>
+    <t>489.5038</t>
+  </si>
+  <si>
+    <t>-0.0156</t>
+  </si>
+  <si>
+    <t>0.0672</t>
+  </si>
+  <si>
+    <t>-0.0767</t>
+  </si>
+  <si>
+    <t>0.6564</t>
+  </si>
+  <si>
+    <t>-0.1296</t>
+  </si>
+  <si>
+    <t>-0.0438</t>
+  </si>
+  <si>
+    <t>-0.9520</t>
+  </si>
+  <si>
+    <t>-7.6390</t>
+  </si>
+  <si>
+    <t>0.7414</t>
+  </si>
+  <si>
+    <t>412.1882-0.0189*B+0.0000*C+0.3475*D-0.1169*E-0.0751*F+0.0000*G-1.2015*H-0.1447*I-0.0289*J-1.2012*K-6.0060*L+0.8229*M</t>
+  </si>
+  <si>
+    <t>412.1882</t>
+  </si>
+  <si>
+    <t>-0.0189</t>
+  </si>
+  <si>
+    <t>0.3475</t>
+  </si>
+  <si>
+    <t>-0.1169</t>
+  </si>
+  <si>
+    <t>-0.0751</t>
+  </si>
+  <si>
+    <t>-1.2015</t>
+  </si>
+  <si>
+    <t>-0.1447</t>
+  </si>
+  <si>
+    <t>-0.0289</t>
+  </si>
+  <si>
+    <t>-1.2012</t>
+  </si>
+  <si>
+    <t>-6.0060</t>
+  </si>
+  <si>
+    <t>0.8229</t>
+  </si>
+  <si>
+    <t>464.6165-0.0175*B+0.0000*C+0.3198*D-0.0852*E-0.0669*F+0.0000*G-0.8038*H-0.1218*I-0.0490*J-1.1498*K-6.2343*L+0.8221*M</t>
+  </si>
+  <si>
+    <t>464.6165</t>
+  </si>
+  <si>
+    <t>-0.0175</t>
+  </si>
+  <si>
+    <t>0.3198</t>
+  </si>
+  <si>
+    <t>-0.0852</t>
+  </si>
+  <si>
+    <t>-0.0669</t>
+  </si>
+  <si>
+    <t>-0.8038</t>
+  </si>
+  <si>
+    <t>-0.1218</t>
+  </si>
+  <si>
+    <t>-0.0490</t>
+  </si>
+  <si>
+    <t>-1.1498</t>
+  </si>
+  <si>
+    <t>-6.2343</t>
+  </si>
+  <si>
+    <t>0.8221</t>
+  </si>
+  <si>
+    <t>218.7731-0.0126*B+0.0000*C+0.4255*D-0.1009*E-0.0520*F+0.0000*G-0.4246*H-0.1154*I-0.0355*J-0.7146*K-8.8593*L+0.9088*M</t>
+  </si>
+  <si>
+    <t>218.7731</t>
+  </si>
+  <si>
+    <t>-0.0126</t>
+  </si>
+  <si>
+    <t>0.4255</t>
+  </si>
+  <si>
+    <t>-0.1009</t>
+  </si>
+  <si>
+    <t>-0.0520</t>
+  </si>
+  <si>
+    <t>-0.4246</t>
+  </si>
+  <si>
+    <t>-0.1154</t>
+  </si>
+  <si>
+    <t>-0.7146</t>
+  </si>
+  <si>
+    <t>-8.8593</t>
+  </si>
+  <si>
+    <t>0.9088</t>
+  </si>
+  <si>
+    <t>492.8152-0.0170*B+0.0000*C+0.3965*D-0.0656*E-0.0491*F+0.0000*G-1.1455*H-0.1266*I-0.0414*J-1.6153*K-7.7155*L+0.8947*M</t>
+  </si>
+  <si>
+    <t>492.8152</t>
+  </si>
+  <si>
+    <t>-0.0170</t>
+  </si>
+  <si>
+    <t>0.3965</t>
+  </si>
+  <si>
+    <t>-0.0656</t>
+  </si>
+  <si>
+    <t>-0.0491</t>
+  </si>
+  <si>
+    <t>-1.1455</t>
+  </si>
+  <si>
+    <t>-0.1266</t>
+  </si>
+  <si>
+    <t>-0.0414</t>
+  </si>
+  <si>
+    <t>-1.6153</t>
+  </si>
+  <si>
+    <t>-7.7155</t>
+  </si>
+  <si>
+    <t>0.8947</t>
+  </si>
+  <si>
+    <t>322.5097-0.0148*B+0.0000*C+0.4594*D-0.0984*E-0.0576*F+0.0000*G-2.7527*H-0.0904*I+0.0044*J-1.1811*K-7.9128*L+0.7920*M</t>
+  </si>
+  <si>
+    <t>322.5097</t>
+  </si>
+  <si>
+    <t>-0.0148</t>
+  </si>
+  <si>
+    <t>0.4594</t>
+  </si>
+  <si>
+    <t>-0.0984</t>
+  </si>
+  <si>
+    <t>-0.0576</t>
+  </si>
+  <si>
+    <t>-2.7527</t>
+  </si>
+  <si>
+    <t>-0.0904</t>
+  </si>
+  <si>
+    <t>0.0044</t>
+  </si>
+  <si>
+    <t>-1.1811</t>
+  </si>
+  <si>
+    <t>-7.9128</t>
+  </si>
+  <si>
+    <t>0.7920</t>
+  </si>
+  <si>
+    <t>290.2309-0.0145*B+0.0000*C+0.3487*D-0.0822*E-0.0812*F+0.0000*G+0.7266*H-0.0988*I-0.0202*J-1.4398*K-6.6619*L+0.8370*M</t>
+  </si>
+  <si>
+    <t>290.2309</t>
+  </si>
+  <si>
+    <t>-0.0145</t>
+  </si>
+  <si>
+    <t>0.3487</t>
+  </si>
+  <si>
+    <t>-0.0822</t>
+  </si>
+  <si>
+    <t>0.7266</t>
+  </si>
+  <si>
+    <t>-0.0988</t>
+  </si>
+  <si>
+    <t>-0.0202</t>
+  </si>
+  <si>
+    <t>-1.4398</t>
+  </si>
+  <si>
+    <t>-6.6619</t>
+  </si>
+  <si>
+    <t>0.8370</t>
+  </si>
+  <si>
+    <t>400.1723-0.0144*B+0.0000*C+0.1336*D-0.0971*E-0.0696*F+0.0000*G-1.2958*H-0.1410*I+0.0052*J-0.8765*K-5.3858*L+0.8179*M</t>
+  </si>
+  <si>
+    <t>400.1723</t>
+  </si>
+  <si>
+    <t>-0.0144</t>
+  </si>
+  <si>
+    <t>0.1336</t>
+  </si>
+  <si>
+    <t>-0.0971</t>
+  </si>
+  <si>
+    <t>-0.0696</t>
+  </si>
+  <si>
+    <t>-1.2958</t>
+  </si>
+  <si>
+    <t>-0.1410</t>
+  </si>
+  <si>
+    <t>0.0052</t>
+  </si>
+  <si>
+    <t>-0.8765</t>
+  </si>
+  <si>
+    <t>-5.3858</t>
+  </si>
+  <si>
+    <t>0.8179</t>
+  </si>
+  <si>
+    <t>414.6740-0.0167*B+0.0000*C+0.4078*D-0.1159*E-0.0763*F+0.0000*G-1.1908*H-0.1046*I+0.0410*J-0.7206*K-5.7045*L+0.7510*M</t>
+  </si>
+  <si>
+    <t>414.6740</t>
+  </si>
+  <si>
+    <t>-0.0167</t>
+  </si>
+  <si>
+    <t>0.4078</t>
+  </si>
+  <si>
+    <t>-0.1159</t>
+  </si>
+  <si>
+    <t>-0.0763</t>
+  </si>
+  <si>
+    <t>-1.1908</t>
+  </si>
+  <si>
+    <t>-0.1046</t>
+  </si>
+  <si>
+    <t>0.0410</t>
+  </si>
+  <si>
+    <t>-0.7206</t>
+  </si>
+  <si>
+    <t>-5.7045</t>
+  </si>
+  <si>
+    <t>0.7510</t>
+  </si>
+  <si>
+    <t>312.2245-0.0177*B+0.0000*C+0.3173*D-0.0623*E-0.0515*F+0.0000*G-2.0944*H-0.1339*I-0.0255*J-0.8781*K-6.1974*L+0.9045*M</t>
+  </si>
+  <si>
+    <t>312.2245</t>
+  </si>
+  <si>
+    <t>-0.0177</t>
+  </si>
+  <si>
+    <t>0.3173</t>
+  </si>
+  <si>
+    <t>-0.0515</t>
+  </si>
+  <si>
+    <t>-2.0944</t>
+  </si>
+  <si>
+    <t>-0.1339</t>
+  </si>
+  <si>
+    <t>-0.0255</t>
+  </si>
+  <si>
+    <t>-0.8781</t>
+  </si>
+  <si>
+    <t>-6.1974</t>
+  </si>
+  <si>
+    <t>0.9045</t>
+  </si>
+  <si>
+    <t>458.1592-0.0130*B+0.0000*C+0.3181*D-0.1249*E-0.0688*F+0.0000*G-1.2939*H-0.0738*I-0.0527*J-1.0892*K-6.8316*L+0.8982*M</t>
+  </si>
+  <si>
+    <t>458.1592</t>
+  </si>
+  <si>
+    <t>-0.0130</t>
+  </si>
+  <si>
+    <t>0.3181</t>
+  </si>
+  <si>
+    <t>-0.1249</t>
+  </si>
+  <si>
+    <t>-0.0688</t>
+  </si>
+  <si>
+    <t>-1.2939</t>
+  </si>
+  <si>
+    <t>-0.0738</t>
+  </si>
+  <si>
+    <t>-0.0527</t>
+  </si>
+  <si>
+    <t>-1.0892</t>
+  </si>
+  <si>
+    <t>-6.8316</t>
+  </si>
+  <si>
+    <t>0.8982</t>
+  </si>
+  <si>
+    <t>365.6045-0.0150*B+0.0000*C+0.0714*D-0.0829*E-0.0483*F+0.0000*G-0.4123*H-0.1118*I+0.0018*J-0.7759*K-5.8997*L+0.8967*M</t>
+  </si>
+  <si>
+    <t>365.6045</t>
+  </si>
+  <si>
+    <t>-0.0150</t>
+  </si>
+  <si>
+    <t>0.0714</t>
+  </si>
+  <si>
+    <t>-0.0829</t>
+  </si>
+  <si>
+    <t>-0.0483</t>
+  </si>
+  <si>
+    <t>-0.4123</t>
+  </si>
+  <si>
+    <t>-0.1118</t>
+  </si>
+  <si>
+    <t>0.0018</t>
+  </si>
+  <si>
+    <t>-0.7759</t>
+  </si>
+  <si>
+    <t>-5.8997</t>
+  </si>
+  <si>
+    <t>0.8967</t>
+  </si>
+  <si>
+    <t>476.8133-0.0172*B+0.0000*C+0.1601*D-0.0692*E-0.0423*F+0.0000*G-1.1653*H-0.1266*I+0.0145*J-1.0908*K-7.0923*L+0.6645*M</t>
+  </si>
+  <si>
+    <t>476.8133</t>
+  </si>
+  <si>
+    <t>-0.0172</t>
+  </si>
+  <si>
+    <t>0.1601</t>
+  </si>
+  <si>
+    <t>-0.0692</t>
+  </si>
+  <si>
+    <t>-0.0423</t>
+  </si>
+  <si>
+    <t>-1.1653</t>
+  </si>
+  <si>
+    <t>0.0145</t>
+  </si>
+  <si>
+    <t>-1.0908</t>
+  </si>
+  <si>
+    <t>-7.0923</t>
+  </si>
+  <si>
+    <t>0.6645</t>
+  </si>
+  <si>
+    <t>380.6242-0.0144*B+0.0000*C+0.1144*D-0.0635*E-0.0728*F+0.0000*G-1.7512*H-0.1258*I-0.0610*J-1.4188*K-7.0734*L+0.7898*M</t>
+  </si>
+  <si>
+    <t>380.6242</t>
+  </si>
+  <si>
+    <t>0.1144</t>
+  </si>
+  <si>
+    <t>-0.0635</t>
+  </si>
+  <si>
+    <t>-0.0728</t>
+  </si>
+  <si>
+    <t>-1.7512</t>
+  </si>
+  <si>
+    <t>-0.1258</t>
+  </si>
+  <si>
+    <t>-0.0610</t>
+  </si>
+  <si>
+    <t>-1.4188</t>
+  </si>
+  <si>
+    <t>-7.0734</t>
+  </si>
+  <si>
+    <t>0.7898</t>
+  </si>
+  <si>
+    <t>362.5206-0.0153*B+0.0000*C+0.0320*D-0.0748*E-0.0555*F+0.0000*G-1.2897*H-0.0982*I-0.0330*J-0.5302*K-5.0027*L+0.9035*M</t>
+  </si>
+  <si>
+    <t>362.5206</t>
+  </si>
+  <si>
+    <t>-0.0153</t>
+  </si>
+  <si>
+    <t>0.0320</t>
+  </si>
+  <si>
+    <t>-0.0748</t>
+  </si>
+  <si>
+    <t>-0.0555</t>
+  </si>
+  <si>
+    <t>-1.2897</t>
+  </si>
+  <si>
+    <t>-0.0982</t>
+  </si>
+  <si>
+    <t>-0.0330</t>
+  </si>
+  <si>
+    <t>-0.5302</t>
+  </si>
+  <si>
+    <t>-5.0027</t>
+  </si>
+  <si>
+    <t>0.9035</t>
+  </si>
+  <si>
+    <t>276.9494-0.0157*B+0.0000*C+0.3036*D-0.0628*E-0.0623*F+0.0000*G+1.1439*H-0.0996*I-0.0505*J-1.1856*K-5.7314*L+0.9078*M</t>
+  </si>
+  <si>
+    <t>276.9494</t>
+  </si>
+  <si>
+    <t>-0.0157</t>
+  </si>
+  <si>
+    <t>0.3036</t>
+  </si>
+  <si>
+    <t>-0.0628</t>
+  </si>
+  <si>
+    <t>1.1439</t>
+  </si>
+  <si>
+    <t>-0.0996</t>
+  </si>
+  <si>
+    <t>-0.0505</t>
+  </si>
+  <si>
+    <t>-1.1856</t>
+  </si>
+  <si>
+    <t>-5.7314</t>
+  </si>
+  <si>
+    <t>0.9078</t>
+  </si>
+  <si>
+    <t>437.4384-0.0160*B+0.0000*C+0.3540*D-0.1211*E-0.0677*F+0.0000*G-0.8605*H-0.0919*I-0.0119*J-1.2876*K-4.8633*L+0.9749*M</t>
+  </si>
+  <si>
+    <t>437.4384</t>
+  </si>
+  <si>
+    <t>-0.0160</t>
+  </si>
+  <si>
+    <t>0.3540</t>
+  </si>
+  <si>
+    <t>-0.1211</t>
+  </si>
+  <si>
+    <t>-0.0677</t>
+  </si>
+  <si>
+    <t>-0.8605</t>
+  </si>
+  <si>
+    <t>-0.0919</t>
+  </si>
+  <si>
+    <t>-0.0119</t>
+  </si>
+  <si>
+    <t>-1.2876</t>
+  </si>
+  <si>
+    <t>-4.8633</t>
+  </si>
+  <si>
+    <t>0.9749</t>
+  </si>
+  <si>
+    <t>536.5278-0.0149*B+0.0000*C+0.4743*D-0.0691*E-0.0571*F+0.0000*G-0.9574*H-0.1204*I-0.0381*J-0.9822*K-7.0383*L+0.8349*M</t>
+  </si>
+  <si>
+    <t>536.5278</t>
+  </si>
+  <si>
+    <t>-0.0149</t>
+  </si>
+  <si>
+    <t>0.4743</t>
+  </si>
+  <si>
+    <t>-0.0691</t>
+  </si>
+  <si>
+    <t>-0.0571</t>
+  </si>
+  <si>
+    <t>-0.9574</t>
+  </si>
+  <si>
+    <t>-0.1204</t>
+  </si>
+  <si>
+    <t>-0.0381</t>
+  </si>
+  <si>
+    <t>-0.9822</t>
+  </si>
+  <si>
+    <t>-7.0383</t>
+  </si>
+  <si>
+    <t>0.8349</t>
+  </si>
+  <si>
+    <t>214.1510-0.0135*B+0.0000*C+0.0345*D-0.0803*E-0.0599*F+0.0000*G-1.1605*H-0.1188*I+0.0019*J-0.8523*K-5.3322*L+0.7713*M</t>
+  </si>
+  <si>
+    <t>214.1510</t>
+  </si>
+  <si>
+    <t>-0.0135</t>
+  </si>
+  <si>
+    <t>0.0345</t>
+  </si>
+  <si>
+    <t>-0.0803</t>
+  </si>
+  <si>
+    <t>-0.0599</t>
+  </si>
+  <si>
+    <t>-1.1605</t>
+  </si>
+  <si>
+    <t>-0.1188</t>
+  </si>
+  <si>
+    <t>0.0019</t>
+  </si>
+  <si>
+    <t>-0.8523</t>
+  </si>
+  <si>
+    <t>-5.3322</t>
+  </si>
+  <si>
+    <t>0.7713</t>
+  </si>
+  <si>
+    <t>479.0605-0.0178*B+0.0000*C+0.2599*D-0.1133*E-0.0530*F+0.0000*G-2.0893*H-0.0880*I-0.0897*J-1.3590*K-6.8513*L+0.8425*M</t>
+  </si>
+  <si>
+    <t>479.0605</t>
+  </si>
+  <si>
+    <t>0.2599</t>
+  </si>
+  <si>
+    <t>-0.1133</t>
+  </si>
+  <si>
+    <t>-0.0530</t>
+  </si>
+  <si>
+    <t>-2.0893</t>
+  </si>
+  <si>
+    <t>-0.0880</t>
+  </si>
+  <si>
+    <t>-0.0897</t>
+  </si>
+  <si>
+    <t>-1.3590</t>
+  </si>
+  <si>
+    <t>-6.8513</t>
+  </si>
+  <si>
+    <t>0.8425</t>
+  </si>
+  <si>
+    <t>501.6963-0.0154*B+0.0000*C+0.2993*D-0.1109*E-0.0652*F+0.0000*G-2.0463*H-0.1117*I-0.0261*J-1.2001*K-5.8450*L+0.8930*M</t>
+  </si>
+  <si>
+    <t>501.6963</t>
+  </si>
+  <si>
+    <t>-0.0154</t>
+  </si>
+  <si>
+    <t>0.2993</t>
+  </si>
+  <si>
+    <t>-0.1109</t>
+  </si>
+  <si>
+    <t>-0.0652</t>
+  </si>
+  <si>
+    <t>-2.0463</t>
+  </si>
+  <si>
+    <t>-0.1117</t>
+  </si>
+  <si>
+    <t>-0.0261</t>
+  </si>
+  <si>
+    <t>-1.2001</t>
+  </si>
+  <si>
+    <t>-5.8450</t>
+  </si>
+  <si>
+    <t>0.8930</t>
+  </si>
+  <si>
+    <t>230.6830-0.0184*B+0.0000*C+0.1318*D-0.1005*E-0.0618*F+0.0000*G-0.9578*H-0.1288*I-0.0412*J-1.2085*K-4.9505*L+0.8060*M</t>
+  </si>
+  <si>
+    <t>230.6830</t>
+  </si>
+  <si>
+    <t>-0.0184</t>
+  </si>
+  <si>
+    <t>0.1318</t>
+  </si>
+  <si>
+    <t>-0.1005</t>
+  </si>
+  <si>
+    <t>-0.0618</t>
+  </si>
+  <si>
+    <t>-0.9578</t>
+  </si>
+  <si>
+    <t>-0.1288</t>
+  </si>
+  <si>
+    <t>-0.0412</t>
+  </si>
+  <si>
+    <t>-1.2085</t>
+  </si>
+  <si>
+    <t>-4.9505</t>
+  </si>
+  <si>
+    <t>0.8060</t>
+  </si>
+  <si>
+    <t>330.3664-0.0143*B+0.0000*C+0.1544*D-0.1290*E-0.0660*F+0.0000*G-1.8886*H-0.1310*I-0.0213*J-0.9727*K-6.2925*L+1.0411*M</t>
+  </si>
+  <si>
+    <t>330.3664</t>
+  </si>
+  <si>
+    <t>-0.0143</t>
+  </si>
+  <si>
+    <t>0.1544</t>
+  </si>
+  <si>
+    <t>-0.1290</t>
+  </si>
+  <si>
+    <t>-0.0660</t>
+  </si>
+  <si>
+    <t>-1.8886</t>
+  </si>
+  <si>
+    <t>-0.1310</t>
+  </si>
+  <si>
+    <t>-0.0213</t>
+  </si>
+  <si>
+    <t>-0.9727</t>
+  </si>
+  <si>
+    <t>-6.2925</t>
+  </si>
+  <si>
+    <t>1.0411</t>
+  </si>
+  <si>
+    <t>349.3882-0.0207*B+0.0000*C+0.1570*D-0.0991*E-0.0573*F+0.0000*G-0.0639*H-0.1048*I-0.1011*J-1.1279*K-6.9536*L+0.7013*M</t>
+  </si>
+  <si>
+    <t>349.3882</t>
+  </si>
+  <si>
+    <t>-0.0207</t>
+  </si>
+  <si>
+    <t>0.1570</t>
+  </si>
+  <si>
+    <t>-0.0991</t>
+  </si>
+  <si>
+    <t>-0.0573</t>
+  </si>
+  <si>
+    <t>-0.0639</t>
+  </si>
+  <si>
+    <t>-0.1048</t>
+  </si>
+  <si>
+    <t>-0.1011</t>
+  </si>
+  <si>
+    <t>-1.1279</t>
+  </si>
+  <si>
+    <t>-6.9536</t>
+  </si>
+  <si>
+    <t>0.7013</t>
+  </si>
+  <si>
+    <t>449.2415-0.0166*B+0.0000*C+0.1190*D-0.0893*E-0.0726*F+0.0000*G-1.0276*H-0.0945*I-0.0377*J-1.3080*K-8.5370*L+0.8491*M</t>
+  </si>
+  <si>
+    <t>449.2415</t>
+  </si>
+  <si>
+    <t>-0.0166</t>
+  </si>
+  <si>
+    <t>0.1190</t>
+  </si>
+  <si>
+    <t>-0.0893</t>
+  </si>
+  <si>
+    <t>-0.0726</t>
+  </si>
+  <si>
+    <t>-1.0276</t>
+  </si>
+  <si>
+    <t>-0.0945</t>
+  </si>
+  <si>
+    <t>-0.0377</t>
+  </si>
+  <si>
+    <t>-1.3080</t>
+  </si>
+  <si>
+    <t>-8.5370</t>
+  </si>
+  <si>
+    <t>0.8491</t>
+  </si>
+  <si>
+    <t>321.8282-0.0164*B+0.0000*C+0.1366*D-0.0970*E-0.0499*F+0.0000*G-1.8820*H-0.1089*I-0.0661*J-1.1482*K-7.1085*L+0.7927*M</t>
+  </si>
+  <si>
+    <t>321.8282</t>
+  </si>
+  <si>
+    <t>-0.0164</t>
+  </si>
+  <si>
+    <t>0.1366</t>
+  </si>
+  <si>
+    <t>-0.0970</t>
+  </si>
+  <si>
+    <t>-0.0499</t>
+  </si>
+  <si>
+    <t>-1.8820</t>
+  </si>
+  <si>
+    <t>-0.1089</t>
+  </si>
+  <si>
+    <t>-0.0661</t>
+  </si>
+  <si>
+    <t>-1.1482</t>
+  </si>
+  <si>
+    <t>-7.1085</t>
+  </si>
+  <si>
+    <t>0.7927</t>
+  </si>
+  <si>
+    <t>375.6155-0.0180*B+0.0000*C+0.1919*D-0.0504*E-0.0711*F+0.0000*G-0.1922*H-0.0689*I-0.0366*J-0.6370*K-8.4040*L+0.9482*M</t>
+  </si>
+  <si>
+    <t>375.6155</t>
+  </si>
+  <si>
+    <t>-0.0180</t>
+  </si>
+  <si>
+    <t>0.1919</t>
+  </si>
+  <si>
+    <t>-0.0504</t>
+  </si>
+  <si>
+    <t>-0.0711</t>
+  </si>
+  <si>
+    <t>-0.1922</t>
+  </si>
+  <si>
+    <t>-0.0689</t>
+  </si>
+  <si>
+    <t>-0.0366</t>
+  </si>
+  <si>
+    <t>-0.6370</t>
+  </si>
+  <si>
+    <t>-8.4040</t>
+  </si>
+  <si>
+    <t>0.9482</t>
+  </si>
+  <si>
+    <t>408.1566-0.0131*B+0.0000*C+0.1276*D-0.0812*E-0.0739*F+0.0000*G-1.4087*H-0.1393*I-0.0312*J-1.2363*K-7.5284*L+0.9098*M</t>
+  </si>
+  <si>
+    <t>408.1566</t>
+  </si>
+  <si>
+    <t>-0.0131</t>
+  </si>
+  <si>
+    <t>0.1276</t>
+  </si>
+  <si>
+    <t>-0.0739</t>
+  </si>
+  <si>
+    <t>-1.4087</t>
+  </si>
+  <si>
+    <t>-0.1393</t>
+  </si>
+  <si>
+    <t>-0.0312</t>
+  </si>
+  <si>
+    <t>-1.2363</t>
+  </si>
+  <si>
+    <t>-7.5284</t>
+  </si>
+  <si>
+    <t>0.9098</t>
+  </si>
+  <si>
+    <t>198.9582-0.0176*B+0.0000*C+0.1225*D-0.0760*E-0.0487*F+0.0000*G-1.3214*H-0.1168*I+0.0110*J-0.8889*K-6.5197*L+0.9374*M</t>
+  </si>
+  <si>
+    <t>198.9582</t>
+  </si>
+  <si>
+    <t>-0.0176</t>
+  </si>
+  <si>
+    <t>0.1225</t>
+  </si>
+  <si>
+    <t>-0.0760</t>
+  </si>
+  <si>
+    <t>-0.0487</t>
+  </si>
+  <si>
+    <t>-1.3214</t>
+  </si>
+  <si>
+    <t>-0.1168</t>
+  </si>
+  <si>
+    <t>0.0110</t>
+  </si>
+  <si>
+    <t>-0.8889</t>
+  </si>
+  <si>
+    <t>-6.5197</t>
+  </si>
+  <si>
+    <t>0.9374</t>
+  </si>
+  <si>
+    <t>399.3455-0.0169*B+0.0000*C+0.3717*D-0.0769*E-0.0686*F+0.0000*G-2.2167*H-0.1097*I-0.0189*J-1.0843*K-7.3139*L+0.8380*M</t>
+  </si>
+  <si>
+    <t>399.3455</t>
+  </si>
+  <si>
+    <t>-0.0169</t>
+  </si>
+  <si>
+    <t>0.3717</t>
+  </si>
+  <si>
+    <t>-0.0686</t>
+  </si>
+  <si>
+    <t>-2.2167</t>
+  </si>
+  <si>
+    <t>-0.1097</t>
+  </si>
+  <si>
+    <t>-1.0843</t>
+  </si>
+  <si>
+    <t>-7.3139</t>
+  </si>
+  <si>
+    <t>0.8380</t>
+  </si>
+  <si>
+    <t>531.4190-0.0149*B+0.0000*C+0.2909*D-0.0874*E-0.0565*F+0.0000*G-1.0160*H-0.0944*I-0.0343*J-0.8424*K-6.3445*L+0.9029*M</t>
+  </si>
+  <si>
+    <t>531.4190</t>
+  </si>
+  <si>
+    <t>0.2909</t>
+  </si>
+  <si>
+    <t>-0.0874</t>
+  </si>
+  <si>
+    <t>-0.0565</t>
+  </si>
+  <si>
+    <t>-1.0160</t>
+  </si>
+  <si>
+    <t>-0.0944</t>
+  </si>
+  <si>
+    <t>-0.0343</t>
+  </si>
+  <si>
+    <t>-0.8424</t>
+  </si>
+  <si>
+    <t>-6.3445</t>
+  </si>
+  <si>
+    <t>0.9029</t>
+  </si>
+  <si>
+    <t>288.2262-0.0164*B+0.0000*C+0.4467*D-0.0422*E-0.0325*F+0.0000*G-0.5004*H-0.1125*I+0.0023*J-1.1407*K-4.9559*L+0.7399*M</t>
+  </si>
+  <si>
+    <t>288.2262</t>
+  </si>
+  <si>
+    <t>0.4467</t>
+  </si>
+  <si>
+    <t>-0.0422</t>
+  </si>
+  <si>
+    <t>-0.0325</t>
+  </si>
+  <si>
+    <t>-0.5004</t>
+  </si>
+  <si>
+    <t>-0.1125</t>
+  </si>
+  <si>
+    <t>0.0023</t>
+  </si>
+  <si>
+    <t>-1.1407</t>
+  </si>
+  <si>
+    <t>-4.9559</t>
+  </si>
+  <si>
+    <t>0.7399</t>
+  </si>
+  <si>
+    <t>454.3178-0.0191*B+0.0000*C+0.2330*D-0.0411*E-0.0812*F+0.0000*G-0.6057*H-0.1166*I+0.0280*J-1.5039*K-8.5165*L+1.0530*M</t>
+  </si>
+  <si>
+    <t>454.3178</t>
+  </si>
+  <si>
+    <t>-0.0191</t>
+  </si>
+  <si>
+    <t>0.2330</t>
+  </si>
+  <si>
+    <t>-0.0411</t>
+  </si>
+  <si>
+    <t>-0.6057</t>
+  </si>
+  <si>
+    <t>-0.1166</t>
+  </si>
+  <si>
+    <t>0.0280</t>
+  </si>
+  <si>
+    <t>-1.5039</t>
+  </si>
+  <si>
+    <t>-8.5165</t>
+  </si>
+  <si>
+    <t>1.0530</t>
+  </si>
+  <si>
+    <t>355.0724-0.0159*B+0.0000*C+0.1828*D-0.0703*E-0.0656*F+0.0000*G-1.3085*H-0.1251*I-0.0216*J-0.8778*K-4.8319*L+0.8864*M</t>
+  </si>
+  <si>
+    <t>355.0724</t>
+  </si>
+  <si>
+    <t>-0.0159</t>
+  </si>
+  <si>
+    <t>0.1828</t>
+  </si>
+  <si>
+    <t>-0.0703</t>
+  </si>
+  <si>
+    <t>-1.3085</t>
+  </si>
+  <si>
+    <t>-0.1251</t>
+  </si>
+  <si>
+    <t>-0.0216</t>
+  </si>
+  <si>
+    <t>-0.8778</t>
+  </si>
+  <si>
+    <t>-4.8319</t>
+  </si>
+  <si>
+    <t>0.8864</t>
+  </si>
+  <si>
+    <t>420.3108-0.0158*B+0.0000*C+0.3850*D-0.1171*E-0.0673*F+0.0000*G-1.5726*H-0.1225*I-0.0202*J-1.0759*K-5.5899*L+0.7302*M</t>
+  </si>
+  <si>
+    <t>420.3108</t>
+  </si>
+  <si>
+    <t>-0.0158</t>
+  </si>
+  <si>
+    <t>0.3850</t>
+  </si>
+  <si>
+    <t>-0.1171</t>
+  </si>
+  <si>
+    <t>-0.0673</t>
+  </si>
+  <si>
+    <t>-1.5726</t>
+  </si>
+  <si>
+    <t>-0.1225</t>
+  </si>
+  <si>
+    <t>-1.0759</t>
+  </si>
+  <si>
+    <t>-5.5899</t>
+  </si>
+  <si>
+    <t>0.7302</t>
+  </si>
+  <si>
+    <t>399.7689-0.0127*B+0.0000*C+0.1254*D-0.0984*E-0.0583*F+0.0000*G-1.8254*H-0.1200*I-0.0482*J-1.0811*K-7.7292*L+1.1034*M</t>
+  </si>
+  <si>
+    <t>399.7689</t>
+  </si>
+  <si>
+    <t>-0.0127</t>
+  </si>
+  <si>
+    <t>0.1254</t>
+  </si>
+  <si>
+    <t>-0.0583</t>
+  </si>
+  <si>
+    <t>-1.8254</t>
+  </si>
+  <si>
+    <t>-0.1200</t>
+  </si>
+  <si>
+    <t>-0.0482</t>
+  </si>
+  <si>
+    <t>-1.0811</t>
+  </si>
+  <si>
+    <t>-7.7292</t>
+  </si>
+  <si>
+    <t>1.1034</t>
+  </si>
+  <si>
+    <t>311.0413-0.0162*B+0.0000*C+0.4316*D-0.0843*E-0.0604*F+0.0000*G-3.2204*H-0.0936*I-0.0116*J-1.0099*K-7.9602*L+0.7831*M</t>
+  </si>
+  <si>
+    <t>311.0413</t>
+  </si>
+  <si>
+    <t>-0.0162</t>
+  </si>
+  <si>
+    <t>0.4316</t>
+  </si>
+  <si>
+    <t>-0.0843</t>
+  </si>
+  <si>
+    <t>-0.0604</t>
+  </si>
+  <si>
+    <t>-3.2204</t>
+  </si>
+  <si>
+    <t>-0.0936</t>
+  </si>
+  <si>
+    <t>-0.0116</t>
+  </si>
+  <si>
+    <t>-1.0099</t>
+  </si>
+  <si>
+    <t>-7.9602</t>
+  </si>
+  <si>
+    <t>0.7831</t>
+  </si>
+  <si>
+    <t>384.0496-0.0136*B+0.0000*C+0.2600*D-0.1386*E-0.0790*F+0.0000*G-1.6984*H-0.0885*I-0.0882*J-1.0303*K-7.0905*L+0.8066*M</t>
+  </si>
+  <si>
+    <t>384.0496</t>
+  </si>
+  <si>
+    <t>-0.0136</t>
+  </si>
+  <si>
+    <t>0.2600</t>
+  </si>
+  <si>
+    <t>-0.1386</t>
+  </si>
+  <si>
+    <t>-0.0790</t>
+  </si>
+  <si>
+    <t>-1.6984</t>
+  </si>
+  <si>
+    <t>-0.0885</t>
+  </si>
+  <si>
+    <t>-0.0882</t>
+  </si>
+  <si>
+    <t>-1.0303</t>
+  </si>
+  <si>
+    <t>-7.0905</t>
+  </si>
+  <si>
+    <t>0.8066</t>
+  </si>
+  <si>
+    <t>467.4114-0.0133*B+0.0000*C+0.2418*D-0.1296*E-0.0510*F+0.0000*G+0.2239*H-0.1236*I-0.0595*J-0.6206*K-7.8137*L+0.9275*M</t>
+  </si>
+  <si>
+    <t>467.4114</t>
+  </si>
+  <si>
+    <t>-0.0133</t>
+  </si>
+  <si>
+    <t>0.2418</t>
+  </si>
+  <si>
+    <t>-0.0510</t>
+  </si>
+  <si>
+    <t>0.2239</t>
+  </si>
+  <si>
+    <t>-0.1236</t>
+  </si>
+  <si>
+    <t>-0.0595</t>
+  </si>
+  <si>
+    <t>-0.6206</t>
+  </si>
+  <si>
+    <t>-7.8137</t>
+  </si>
+  <si>
+    <t>0.9275</t>
+  </si>
+  <si>
+    <t>420.9868-0.0140*B+0.0000*C+0.2346*D-0.0672*E-0.0806*F+0.0000*G-2.1053*H-0.1244*I-0.0509*J-1.0286*K-5.8389*L+0.8903*M</t>
+  </si>
+  <si>
+    <t>420.9868</t>
+  </si>
+  <si>
+    <t>-0.0140</t>
+  </si>
+  <si>
+    <t>0.2346</t>
+  </si>
+  <si>
+    <t>-0.0672</t>
+  </si>
+  <si>
+    <t>-0.0806</t>
+  </si>
+  <si>
+    <t>-2.1053</t>
+  </si>
+  <si>
+    <t>-0.1244</t>
+  </si>
+  <si>
+    <t>-0.0509</t>
+  </si>
+  <si>
+    <t>-1.0286</t>
+  </si>
+  <si>
+    <t>-5.8389</t>
+  </si>
+  <si>
+    <t>0.8903</t>
+  </si>
+  <si>
+    <t>270.9630-0.0154*B+0.0000*C+0.1607*D-0.1087*E-0.0461*F+0.0000*G-1.4317*H-0.1052*I-0.0584*J-0.8505*K-7.2745*L+0.7645*M</t>
+  </si>
+  <si>
+    <t>270.9630</t>
+  </si>
+  <si>
+    <t>0.1607</t>
+  </si>
+  <si>
+    <t>-0.1087</t>
+  </si>
+  <si>
+    <t>-0.0461</t>
+  </si>
+  <si>
+    <t>-1.4317</t>
+  </si>
+  <si>
+    <t>-0.1052</t>
+  </si>
+  <si>
+    <t>-0.0584</t>
+  </si>
+  <si>
+    <t>-0.8505</t>
+  </si>
+  <si>
+    <t>-7.2745</t>
+  </si>
+  <si>
+    <t>0.7645</t>
+  </si>
+  <si>
+    <t>332.7364-0.0140*B+0.0000*C+0.4067*D-0.0696*E-0.0800*F+0.0000*G-1.4536*H-0.0628*I-0.0155*J-1.1032*K-6.2341*L+0.7196*M</t>
+  </si>
+  <si>
+    <t>332.7364</t>
+  </si>
+  <si>
+    <t>0.4067</t>
+  </si>
+  <si>
+    <t>-0.0800</t>
+  </si>
+  <si>
+    <t>-1.4536</t>
+  </si>
+  <si>
+    <t>-0.0155</t>
+  </si>
+  <si>
+    <t>-1.1032</t>
+  </si>
+  <si>
+    <t>-6.2341</t>
+  </si>
+  <si>
+    <t>0.7196</t>
+  </si>
+  <si>
+    <t>374.7495-0.0171*B+0.0000*C+0.1909*D-0.0717*E-0.0501*F+0.0000*G-2.1285*H-0.1332*I-0.0146*J-0.9265*K-5.6977*L+0.7307*M</t>
+  </si>
+  <si>
+    <t>374.7495</t>
+  </si>
+  <si>
+    <t>-0.0171</t>
+  </si>
+  <si>
+    <t>0.1909</t>
+  </si>
+  <si>
+    <t>-0.0717</t>
+  </si>
+  <si>
+    <t>-0.0501</t>
+  </si>
+  <si>
+    <t>-2.1285</t>
+  </si>
+  <si>
+    <t>-0.1332</t>
+  </si>
+  <si>
+    <t>-0.0146</t>
+  </si>
+  <si>
+    <t>-0.9265</t>
+  </si>
+  <si>
+    <t>-5.6977</t>
+  </si>
+  <si>
+    <t>0.7307</t>
+  </si>
+  <si>
+    <t>451.0095-0.0169*B+0.0000*C+0.3276*D-0.0730*E-0.0604*F+0.0000*G-1.9847*H-0.1281*I-0.0527*J-1.2733*K-6.1641*L+0.8096*M</t>
+  </si>
+  <si>
+    <t>451.0095</t>
+  </si>
+  <si>
+    <t>0.3276</t>
+  </si>
+  <si>
+    <t>-0.0730</t>
+  </si>
+  <si>
+    <t>-1.9847</t>
+  </si>
+  <si>
+    <t>-0.1281</t>
+  </si>
+  <si>
+    <t>-1.2733</t>
+  </si>
+  <si>
+    <t>-6.1641</t>
+  </si>
+  <si>
+    <t>0.8096</t>
+  </si>
+  <si>
+    <t>404.8756-0.0160*B+0.0000*C+0.2374*D-0.0851*E-0.0621*F+0.0000*G-0.7706*H-0.1308*I-0.0595*J-1.1851*K-10.2000*L+0.9762*M</t>
+  </si>
+  <si>
+    <t>404.8756</t>
+  </si>
+  <si>
+    <t>0.2374</t>
+  </si>
+  <si>
+    <t>-0.0851</t>
+  </si>
+  <si>
+    <t>-0.7706</t>
+  </si>
+  <si>
+    <t>-0.1308</t>
+  </si>
+  <si>
+    <t>-1.1851</t>
+  </si>
+  <si>
+    <t>-10.2000</t>
+  </si>
+  <si>
+    <t>0.9762</t>
+  </si>
+  <si>
+    <t>332.0023-0.0155*B+0.0000*C+0.1767*D-0.1041*E-0.0728*F+0.0000*G-0.5330*H-0.1002*I-0.0253*J-0.7149*K-5.6547*L+0.7904*M</t>
+  </si>
+  <si>
+    <t>332.0023</t>
+  </si>
+  <si>
+    <t>0.1767</t>
+  </si>
+  <si>
+    <t>-0.1041</t>
+  </si>
+  <si>
+    <t>-0.5330</t>
+  </si>
+  <si>
+    <t>-0.1002</t>
+  </si>
+  <si>
+    <t>-0.0253</t>
+  </si>
+  <si>
+    <t>-0.7149</t>
+  </si>
+  <si>
+    <t>-5.6547</t>
+  </si>
+  <si>
+    <t>0.7904</t>
+  </si>
+  <si>
+    <t>395.8238-0.0163*B+0.0000*C+0.4374*D-0.0814*E-0.0830*F+0.0000*G+1.2293*H-0.1328*I+0.0399*J-0.9939*K-6.3759*L+0.8658*M</t>
+  </si>
+  <si>
+    <t>395.8238</t>
+  </si>
+  <si>
+    <t>-0.0163</t>
+  </si>
+  <si>
+    <t>0.4374</t>
+  </si>
+  <si>
+    <t>-0.0814</t>
+  </si>
+  <si>
+    <t>-0.0830</t>
+  </si>
+  <si>
+    <t>1.2293</t>
+  </si>
+  <si>
+    <t>-0.1328</t>
+  </si>
+  <si>
+    <t>0.0399</t>
+  </si>
+  <si>
+    <t>-0.9939</t>
+  </si>
+  <si>
+    <t>-6.3759</t>
+  </si>
+  <si>
+    <t>0.8658</t>
+  </si>
+  <si>
+    <t>379.3477-0.0144*B+0.0000*C+0.1936*D-0.1186*E-0.0570*F+0.0000*G-0.7379*H-0.1067*I+0.0122*J-0.8799*K-5.7238*L+0.8498*M</t>
+  </si>
+  <si>
+    <t>379.3477</t>
+  </si>
+  <si>
+    <t>0.1936</t>
+  </si>
+  <si>
+    <t>-0.1186</t>
+  </si>
+  <si>
+    <t>-0.0570</t>
+  </si>
+  <si>
+    <t>-0.7379</t>
+  </si>
+  <si>
+    <t>-0.1067</t>
+  </si>
+  <si>
+    <t>0.0122</t>
+  </si>
+  <si>
+    <t>-0.8799</t>
+  </si>
+  <si>
+    <t>-5.7238</t>
+  </si>
+  <si>
+    <t>0.8498</t>
+  </si>
+  <si>
+    <t>321.0414-0.0168*B+0.0000*C+0.2445*D-0.1013*E-0.0556*F+0.0000*G-0.3493*H-0.0958*I+0.0194*J-1.2242*K-9.3792*L+0.8389*M</t>
+  </si>
+  <si>
+    <t>321.0414</t>
+  </si>
+  <si>
+    <t>-0.0168</t>
+  </si>
+  <si>
+    <t>0.2445</t>
+  </si>
+  <si>
+    <t>-0.1013</t>
+  </si>
+  <si>
+    <t>-0.0556</t>
+  </si>
+  <si>
+    <t>-0.3493</t>
+  </si>
+  <si>
+    <t>-0.0958</t>
+  </si>
+  <si>
+    <t>0.0194</t>
+  </si>
+  <si>
+    <t>-1.2242</t>
+  </si>
+  <si>
+    <t>-9.3792</t>
+  </si>
+  <si>
+    <t>0.8389</t>
+  </si>
+  <si>
+    <t>473.1298-0.0170*B+0.0000*C+0.2067*D-0.0834*E-0.0633*F+0.0000*G-0.4801*H-0.1057*I-0.0756*J-0.5231*K-5.4760*L+0.8401*M</t>
+  </si>
+  <si>
+    <t>473.1298</t>
+  </si>
+  <si>
+    <t>0.2067</t>
+  </si>
+  <si>
+    <t>-0.0834</t>
+  </si>
+  <si>
+    <t>-0.0633</t>
+  </si>
+  <si>
+    <t>-0.4801</t>
+  </si>
+  <si>
+    <t>-0.1057</t>
+  </si>
+  <si>
+    <t>-0.0756</t>
+  </si>
+  <si>
+    <t>-0.5231</t>
+  </si>
+  <si>
+    <t>-5.4760</t>
+  </si>
+  <si>
+    <t>0.8401</t>
+  </si>
+  <si>
+    <t>403.4310-0.0177*B+0.0000*C+0.0995*D-0.1061*E-0.0530*F+0.0000*G+0.8966*H-0.0904*I-0.0365*J-0.8264*K-4.4026*L+0.7703*M</t>
+  </si>
+  <si>
+    <t>403.4310</t>
+  </si>
+  <si>
+    <t>0.0995</t>
+  </si>
+  <si>
+    <t>-0.1061</t>
+  </si>
+  <si>
+    <t>0.8966</t>
+  </si>
+  <si>
+    <t>-0.0365</t>
+  </si>
+  <si>
+    <t>-0.8264</t>
+  </si>
+  <si>
+    <t>-4.4026</t>
+  </si>
+  <si>
+    <t>0.7703</t>
+  </si>
+  <si>
+    <t>485.6327-0.0140*B+0.0000*C+0.1388*D-0.0702*E-0.0370*F+0.0000*G-1.2892*H-0.0886*I-0.0368*J-0.7484*K-7.5156*L+0.7991*M</t>
+  </si>
+  <si>
+    <t>485.6327</t>
+  </si>
+  <si>
+    <t>0.1388</t>
+  </si>
+  <si>
+    <t>-0.0702</t>
+  </si>
+  <si>
+    <t>-0.0370</t>
+  </si>
+  <si>
+    <t>-1.2892</t>
+  </si>
+  <si>
+    <t>-0.0886</t>
+  </si>
+  <si>
+    <t>-0.0368</t>
+  </si>
+  <si>
+    <t>-0.7484</t>
+  </si>
+  <si>
+    <t>-7.5156</t>
+  </si>
+  <si>
+    <t>0.7991</t>
+  </si>
+  <si>
+    <t>421.1535-0.0129*B+0.0000*C+0.3858*D-0.0936*E-0.0502*F+0.0000*G-0.1170*H-0.0769*I-0.0405*J-1.1600*K-4.5133*L+0.7330*M</t>
+  </si>
+  <si>
+    <t>421.1535</t>
+  </si>
+  <si>
+    <t>-0.0129</t>
+  </si>
+  <si>
+    <t>0.3858</t>
+  </si>
+  <si>
+    <t>-0.0502</t>
+  </si>
+  <si>
+    <t>-0.1170</t>
+  </si>
+  <si>
+    <t>-0.0405</t>
+  </si>
+  <si>
+    <t>-1.1600</t>
+  </si>
+  <si>
+    <t>-4.5133</t>
+  </si>
+  <si>
+    <t>0.7330</t>
+  </si>
+  <si>
+    <t>351.0493-0.0172*B+0.0000*C+0.2748*D-0.1026*E-0.0696*F+0.0000*G-0.4343*H-0.0771*I-0.0044*J-0.8253*K-6.5797*L+0.8669*M</t>
+  </si>
+  <si>
+    <t>351.0493</t>
+  </si>
+  <si>
+    <t>0.2748</t>
+  </si>
+  <si>
+    <t>-0.1026</t>
+  </si>
+  <si>
+    <t>-0.4343</t>
+  </si>
+  <si>
+    <t>-0.0771</t>
+  </si>
+  <si>
+    <t>-0.0044</t>
+  </si>
+  <si>
+    <t>-0.8253</t>
+  </si>
+  <si>
+    <t>-6.5797</t>
+  </si>
+  <si>
+    <t>0.8669</t>
+  </si>
+  <si>
+    <t>369.8651-0.0165*B+0.0000*C+0.0906*D-0.0916*E-0.0619*F+0.0000*G+0.0129*H-0.1043*I-0.0342*J-1.3942*K-9.0586*L+0.8322*M</t>
+  </si>
+  <si>
+    <t>369.8651</t>
+  </si>
+  <si>
+    <t>-0.0165</t>
+  </si>
+  <si>
+    <t>0.0906</t>
+  </si>
+  <si>
+    <t>-0.0916</t>
+  </si>
+  <si>
+    <t>-0.0619</t>
+  </si>
+  <si>
+    <t>0.0129</t>
+  </si>
+  <si>
+    <t>-0.1043</t>
+  </si>
+  <si>
+    <t>-0.0342</t>
+  </si>
+  <si>
+    <t>-1.3942</t>
+  </si>
+  <si>
+    <t>-9.0586</t>
+  </si>
+  <si>
+    <t>0.8322</t>
+  </si>
+  <si>
+    <t>361.7186-0.0154*B+0.0000*C+0.1557*D-0.0769*E-0.0723*F+0.0000*G+0.1243*H-0.0870*I-0.1082*J-1.0572*K-8.6033*L+0.8240*M</t>
+  </si>
+  <si>
+    <t>361.7186</t>
+  </si>
+  <si>
+    <t>0.1557</t>
+  </si>
+  <si>
+    <t>-0.0723</t>
+  </si>
+  <si>
+    <t>0.1243</t>
+  </si>
+  <si>
+    <t>-0.0870</t>
+  </si>
+  <si>
+    <t>-0.1082</t>
+  </si>
+  <si>
+    <t>-1.0572</t>
+  </si>
+  <si>
+    <t>-8.6033</t>
+  </si>
+  <si>
+    <t>0.8240</t>
+  </si>
+  <si>
+    <t>265.9302-0.0207*B+0.0000*C+0.2283*D-0.0772*E-0.0604*F+0.0000*G+1.0231*H-0.0946*I-0.0429*J-1.2769*K-7.3150*L+0.7857*M</t>
+  </si>
+  <si>
+    <t>265.9302</t>
+  </si>
+  <si>
+    <t>0.2283</t>
+  </si>
+  <si>
+    <t>-0.0772</t>
+  </si>
+  <si>
+    <t>1.0231</t>
+  </si>
+  <si>
+    <t>-0.0946</t>
+  </si>
+  <si>
+    <t>-0.0429</t>
+  </si>
+  <si>
+    <t>-1.2769</t>
+  </si>
+  <si>
+    <t>-7.3150</t>
+  </si>
+  <si>
+    <t>0.7857</t>
+  </si>
+  <si>
+    <t>427.2256-0.0165*B+0.0000*C+0.2567*D-0.0753*E-0.0598*F+0.0000*G-1.5363*H-0.1002*I+0.0093*J-1.5705*K-3.8559*L+0.7512*M</t>
+  </si>
+  <si>
+    <t>427.2256</t>
+  </si>
+  <si>
+    <t>0.2567</t>
+  </si>
+  <si>
+    <t>-0.0753</t>
+  </si>
+  <si>
+    <t>-0.0598</t>
+  </si>
+  <si>
+    <t>-1.5363</t>
+  </si>
+  <si>
+    <t>0.0093</t>
+  </si>
+  <si>
+    <t>-1.5705</t>
+  </si>
+  <si>
+    <t>-3.8559</t>
+  </si>
+  <si>
+    <t>0.7512</t>
+  </si>
+  <si>
+    <t>274.3488-0.0140*B+0.0000*C+0.2568*D-0.0820*E-0.0549*F+0.0000*G-0.3530*H-0.0984*I-0.0265*J-1.6762*K-5.5408*L+0.8824*M</t>
+  </si>
+  <si>
+    <t>274.3488</t>
+  </si>
+  <si>
+    <t>0.2568</t>
+  </si>
+  <si>
+    <t>-0.0549</t>
+  </si>
+  <si>
+    <t>-0.3530</t>
+  </si>
+  <si>
+    <t>-0.0265</t>
+  </si>
+  <si>
+    <t>-1.6762</t>
+  </si>
+  <si>
+    <t>-5.5408</t>
+  </si>
+  <si>
+    <t>0.8824</t>
+  </si>
+  <si>
+    <t>338.1853-0.0169*B+0.0000*C+0.2822*D-0.0985*E-0.0766*F+0.0000*G-2.5994*H-0.1025*I-0.0209*J-0.6553*K-7.9171*L+0.9170*M</t>
+  </si>
+  <si>
+    <t>338.1853</t>
+  </si>
+  <si>
+    <t>0.2822</t>
+  </si>
+  <si>
+    <t>-0.0985</t>
+  </si>
+  <si>
+    <t>-0.0766</t>
+  </si>
+  <si>
+    <t>-2.5994</t>
+  </si>
+  <si>
+    <t>-0.1025</t>
+  </si>
+  <si>
+    <t>-0.0209</t>
+  </si>
+  <si>
+    <t>-0.6553</t>
+  </si>
+  <si>
+    <t>-7.9171</t>
+  </si>
+  <si>
+    <t>0.9170</t>
+  </si>
+  <si>
+    <t>386.0797-0.0179*B+0.0000*C+0.2583*D-0.0725*E-0.0435*F+0.0000*G-2.2714*H-0.1380*I+0.0028*J-1.1563*K-6.3103*L+0.8006*M</t>
+  </si>
+  <si>
+    <t>386.0797</t>
+  </si>
+  <si>
+    <t>-0.0179</t>
+  </si>
+  <si>
+    <t>0.2583</t>
+  </si>
+  <si>
+    <t>-0.0725</t>
+  </si>
+  <si>
+    <t>-0.0435</t>
+  </si>
+  <si>
+    <t>-2.2714</t>
+  </si>
+  <si>
+    <t>-0.1380</t>
+  </si>
+  <si>
+    <t>0.0028</t>
+  </si>
+  <si>
+    <t>-1.1563</t>
+  </si>
+  <si>
+    <t>-6.3103</t>
+  </si>
+  <si>
+    <t>0.8006</t>
+  </si>
+  <si>
+    <t>399.7536-0.0184*B+0.0000*C+0.5482*D-0.0940*E-0.0645*F+0.0000*G-2.1952*H-0.1067*I-0.0136*J-0.9291*K-6.8556*L+0.7495*M</t>
+  </si>
+  <si>
+    <t>399.7536</t>
+  </si>
+  <si>
+    <t>0.5482</t>
+  </si>
+  <si>
+    <t>-0.0940</t>
+  </si>
+  <si>
+    <t>-0.0645</t>
+  </si>
+  <si>
+    <t>-2.1952</t>
+  </si>
+  <si>
+    <t>-0.9291</t>
+  </si>
+  <si>
+    <t>-6.8556</t>
+  </si>
+  <si>
+    <t>0.7495</t>
+  </si>
+  <si>
+    <t>423.7577-0.0163*B+0.0000*C+0.0737*D-0.1080*E-0.0668*F+0.0000*G-1.6546*H-0.1447*I-0.0130*J-0.9761*K-7.3335*L+0.8535*M</t>
+  </si>
+  <si>
+    <t>423.7577</t>
+  </si>
+  <si>
+    <t>0.0737</t>
+  </si>
+  <si>
+    <t>-0.1080</t>
+  </si>
+  <si>
+    <t>-0.0668</t>
+  </si>
+  <si>
+    <t>-1.6546</t>
+  </si>
+  <si>
+    <t>-0.9761</t>
+  </si>
+  <si>
+    <t>-7.3335</t>
+  </si>
+  <si>
+    <t>0.8535</t>
+  </si>
+  <si>
+    <t>394.5303-0.0164*B+0.0000*C+0.1930*D-0.0970*E-0.0579*F+0.0000*G-1.2447*H-0.0947*I-0.0347*J-1.1352*K-5.7930*L+0.8187*M</t>
+  </si>
+  <si>
+    <t>394.5303</t>
+  </si>
+  <si>
+    <t>0.1930</t>
+  </si>
+  <si>
+    <t>-0.0579</t>
+  </si>
+  <si>
+    <t>-1.2447</t>
+  </si>
+  <si>
+    <t>-0.0947</t>
+  </si>
+  <si>
+    <t>-0.0347</t>
+  </si>
+  <si>
+    <t>-1.1352</t>
+  </si>
+  <si>
+    <t>-5.7930</t>
+  </si>
+  <si>
+    <t>0.8187</t>
+  </si>
+  <si>
+    <t>346.5363-0.0175*B+0.0000*C+0.3492*D-0.0672*E-0.0599*F+0.0000*G-1.9912*H-0.0662*I+0.0251*J-0.6946*K-5.8742*L+0.8083*M</t>
+  </si>
+  <si>
+    <t>346.5363</t>
+  </si>
+  <si>
+    <t>0.3492</t>
+  </si>
+  <si>
+    <t>-1.9912</t>
+  </si>
+  <si>
+    <t>-0.0662</t>
+  </si>
+  <si>
+    <t>0.0251</t>
+  </si>
+  <si>
+    <t>-0.6946</t>
+  </si>
+  <si>
+    <t>-5.8742</t>
+  </si>
+  <si>
+    <t>0.8083</t>
+  </si>
+  <si>
+    <t>450.1454-0.0150*B+0.0000*C+0.2643*D-0.0957*E-0.0613*F+0.0000*G-1.7794*H-0.0924*I-0.0358*J-0.4057*K-7.2821*L+0.8486*M</t>
+  </si>
+  <si>
+    <t>450.1454</t>
+  </si>
+  <si>
+    <t>0.2643</t>
+  </si>
+  <si>
+    <t>-0.0957</t>
+  </si>
+  <si>
+    <t>-0.0613</t>
+  </si>
+  <si>
+    <t>-1.7794</t>
+  </si>
+  <si>
+    <t>-0.0924</t>
+  </si>
+  <si>
+    <t>-0.0358</t>
+  </si>
+  <si>
+    <t>-0.4057</t>
+  </si>
+  <si>
+    <t>-7.2821</t>
+  </si>
+  <si>
+    <t>0.8486</t>
+  </si>
+  <si>
+    <t>534.4909-0.0174*B+0.0000*C+0.3630*D-0.1094*E-0.0602*F+0.0000*G-1.1290*H-0.1107*I+0.0243*J-0.6419*K-5.4396*L+0.8253*M</t>
+  </si>
+  <si>
+    <t>534.4909</t>
+  </si>
+  <si>
+    <t>-0.0174</t>
+  </si>
+  <si>
+    <t>0.3630</t>
+  </si>
+  <si>
+    <t>-0.1094</t>
+  </si>
+  <si>
+    <t>-0.0602</t>
+  </si>
+  <si>
+    <t>-1.1290</t>
+  </si>
+  <si>
+    <t>-0.1107</t>
+  </si>
+  <si>
+    <t>0.0243</t>
+  </si>
+  <si>
+    <t>-0.6419</t>
+  </si>
+  <si>
+    <t>-5.4396</t>
+  </si>
+  <si>
+    <t>0.8253</t>
+  </si>
+  <si>
+    <t>256.3976-0.0142*B+0.0000*C+0.2263*D-0.1037*E-0.0586*F+0.0000*G-0.7950*H-0.1106*I-0.0130*J-0.3691*K-6.9811*L+0.9367*M</t>
+  </si>
+  <si>
+    <t>256.3976</t>
+  </si>
+  <si>
+    <t>-0.0142</t>
+  </si>
+  <si>
+    <t>0.2263</t>
+  </si>
+  <si>
+    <t>-0.1037</t>
+  </si>
+  <si>
+    <t>-0.0586</t>
+  </si>
+  <si>
+    <t>-0.7950</t>
+  </si>
+  <si>
+    <t>-0.1106</t>
+  </si>
+  <si>
+    <t>-0.3691</t>
+  </si>
+  <si>
+    <t>-6.9811</t>
+  </si>
+  <si>
+    <t>0.9367</t>
+  </si>
+  <si>
+    <t>540.4338-0.0146*B+0.0000*C+0.2600*D-0.0585*E-0.0601*F+0.0000*G-0.5781*H-0.1319*I-0.0307*J-0.6150*K-6.3629*L+1.0180*M</t>
+  </si>
+  <si>
+    <t>540.4338</t>
+  </si>
+  <si>
+    <t>-0.0585</t>
+  </si>
+  <si>
+    <t>-0.0601</t>
+  </si>
+  <si>
+    <t>-0.5781</t>
+  </si>
+  <si>
+    <t>-0.1319</t>
+  </si>
+  <si>
+    <t>-0.0307</t>
+  </si>
+  <si>
+    <t>-0.6150</t>
+  </si>
+  <si>
+    <t>-6.3629</t>
+  </si>
+  <si>
+    <t>1.0180</t>
+  </si>
+  <si>
+    <t>399.4466-0.0139*B+0.0000*C+0.1418*D-0.0893*E-0.0651*F+0.0000*G-0.9260*H-0.0947*I-0.0468*J-1.3158*K-6.4065*L+0.8989*M</t>
+  </si>
+  <si>
+    <t>399.4466</t>
+  </si>
+  <si>
+    <t>-0.0139</t>
+  </si>
+  <si>
+    <t>0.1418</t>
+  </si>
+  <si>
+    <t>-0.0651</t>
+  </si>
+  <si>
+    <t>-0.9260</t>
+  </si>
+  <si>
+    <t>-0.0468</t>
+  </si>
+  <si>
+    <t>-1.3158</t>
+  </si>
+  <si>
+    <t>-6.4065</t>
+  </si>
+  <si>
+    <t>0.8989</t>
+  </si>
+  <si>
+    <t>517.2685-0.0181*B+0.0000*C+0.0200*D-0.0977*E-0.0464*F+0.0000*G-2.3272*H-0.1174*I+0.0277*J-1.0804*K-6.5377*L+0.8520*M</t>
+  </si>
+  <si>
+    <t>517.2685</t>
+  </si>
+  <si>
+    <t>-0.0181</t>
+  </si>
+  <si>
+    <t>0.0200</t>
+  </si>
+  <si>
+    <t>-0.0977</t>
+  </si>
+  <si>
+    <t>-0.0464</t>
+  </si>
+  <si>
+    <t>-2.3272</t>
+  </si>
+  <si>
+    <t>-0.1174</t>
+  </si>
+  <si>
+    <t>0.0277</t>
+  </si>
+  <si>
+    <t>-1.0804</t>
+  </si>
+  <si>
+    <t>-6.5377</t>
+  </si>
+  <si>
+    <t>0.8520</t>
+  </si>
+  <si>
+    <t>455.0171-0.0159*B+0.0000*C+0.0209*D-0.0880*E-0.0572*F+0.0000*G-3.7929*H-0.0844*I-0.0355*J-1.4525*K-7.1745*L+0.9950*M</t>
+  </si>
+  <si>
+    <t>455.0171</t>
+  </si>
+  <si>
+    <t>0.0209</t>
+  </si>
+  <si>
+    <t>-0.0572</t>
+  </si>
+  <si>
+    <t>-3.7929</t>
+  </si>
+  <si>
+    <t>-0.0844</t>
+  </si>
+  <si>
+    <t>-1.4525</t>
+  </si>
+  <si>
+    <t>-7.1745</t>
+  </si>
+  <si>
+    <t>0.9950</t>
+  </si>
+  <si>
+    <t>455.7776-0.0153*B+0.0000*C+0.2173*D-0.1391*E-0.0617*F+0.0000*G+0.0658*H-0.1233*I-0.0083*J-1.2141*K-5.6106*L+0.7096*M</t>
+  </si>
+  <si>
+    <t>455.7776</t>
+  </si>
+  <si>
+    <t>0.2173</t>
+  </si>
+  <si>
+    <t>-0.1391</t>
+  </si>
+  <si>
+    <t>-0.0617</t>
+  </si>
+  <si>
+    <t>0.0658</t>
+  </si>
+  <si>
+    <t>-0.1233</t>
+  </si>
+  <si>
+    <t>-0.0083</t>
+  </si>
+  <si>
+    <t>-1.2141</t>
+  </si>
+  <si>
+    <t>-5.6106</t>
+  </si>
+  <si>
+    <t>0.7096</t>
+  </si>
+  <si>
+    <t>421.8773-0.0185*B+0.0000*C+0.0515*D-0.0968*E-0.0646*F+0.0000*G-0.9179*H-0.1253*I-0.0449*J-1.0212*K-4.8237*L+0.9365*M</t>
+  </si>
+  <si>
+    <t>421.8773</t>
+  </si>
+  <si>
+    <t>-0.0185</t>
+  </si>
+  <si>
+    <t>0.0515</t>
+  </si>
+  <si>
+    <t>-0.0968</t>
+  </si>
+  <si>
+    <t>-0.0646</t>
+  </si>
+  <si>
+    <t>-0.9179</t>
+  </si>
+  <si>
+    <t>-0.1253</t>
+  </si>
+  <si>
+    <t>-0.0449</t>
+  </si>
+  <si>
+    <t>-1.0212</t>
+  </si>
+  <si>
+    <t>-4.8237</t>
+  </si>
+  <si>
+    <t>0.9365</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>120</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1557,8 +4462,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1568,12 +4474,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{1C87F38B-8B09-47E1-A0A6-D5B12A61D915}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1875,7 +4782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O121"/>
   <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
     <col min="2" max="2" width="18.53515625" customWidth="1"/>
@@ -3809,8 +6716,3768 @@
         <v>370</v>
       </c>
     </row>
+    <row r="42" spans="1:15">
+      <c r="A42" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="I42" s="2">
+        <v>0</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="I43" s="2">
+        <v>0</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E44" s="2">
+        <v>0</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="I44" s="2">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="I45" s="2">
+        <v>0</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E46" s="2">
+        <v>0</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="I46" s="2">
+        <v>0</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E47" s="2">
+        <v>0</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="I47" s="2">
+        <v>0</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="A48" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="E48" s="2">
+        <v>0</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="I48" s="2">
+        <v>0</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E49" s="2">
+        <v>0</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="I49" s="2">
+        <v>0</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
+      <c r="A50" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="E50" s="2">
+        <v>0</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="I50" s="2">
+        <v>0</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="E51" s="2">
+        <v>0</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="I51" s="2">
+        <v>0</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="N51" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
+      <c r="A52" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="E52" s="2">
+        <v>0</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="I52" s="2">
+        <v>0</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="E53" s="2">
+        <v>0</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="I53" s="2">
+        <v>0</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
+      <c r="A54" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="E54" s="2">
+        <v>0</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="I54" s="2">
+        <v>0</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
+      <c r="A55" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="E55" s="2">
+        <v>0</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="I55" s="2">
+        <v>0</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
+      <c r="A56" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="E56" s="2">
+        <v>0</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="I56" s="2">
+        <v>0</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
+      <c r="A57" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="E57" s="2">
+        <v>0</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="I57" s="2">
+        <v>0</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
+      <c r="A58" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="E58" s="2">
+        <v>0</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="I58" s="2">
+        <v>0</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15">
+      <c r="A59" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="E59" s="2">
+        <v>0</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="I59" s="2">
+        <v>0</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15">
+      <c r="A60" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="E60" s="2">
+        <v>0</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="I60" s="2">
+        <v>0</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="A61" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="E61" s="2">
+        <v>0</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="I61" s="2">
+        <v>0</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15">
+      <c r="A62" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="E62" s="2">
+        <v>0</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="I62" s="2">
+        <v>0</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="M62" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
+      <c r="A63" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="E63" s="2">
+        <v>0</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="I63" s="2">
+        <v>0</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="N63" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15">
+      <c r="A64" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="E64" s="2">
+        <v>0</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="I64" s="2">
+        <v>0</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="N64" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
+      <c r="A65" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="E65" s="2">
+        <v>0</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="I65" s="2">
+        <v>0</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="N65" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
+      <c r="A66" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="E66" s="2">
+        <v>0</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="I66" s="2">
+        <v>0</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
+      <c r="A67" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E67" s="2">
+        <v>0</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="I67" s="2">
+        <v>0</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="N67" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15">
+      <c r="A68" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="E68" s="2">
+        <v>0</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="I68" s="2">
+        <v>0</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
+      <c r="A69" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="E69" s="2">
+        <v>0</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="I69" s="2">
+        <v>0</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="N69" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
+      <c r="A70" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="E70" s="2">
+        <v>0</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="I70" s="2">
+        <v>0</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="N70" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
+      <c r="A71" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="E71" s="2">
+        <v>0</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="I71" s="2">
+        <v>0</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="N71" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15">
+      <c r="A72" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="E72" s="2">
+        <v>0</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="I72" s="2">
+        <v>0</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="N72" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
+      <c r="A73" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="E73" s="2">
+        <v>0</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="I73" s="2">
+        <v>0</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="N73" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="O73" s="1" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
+      <c r="A74" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="E74" s="2">
+        <v>0</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="I74" s="2">
+        <v>0</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="M74" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="N74" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="O74" s="1" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
+      <c r="A75" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="E75" s="2">
+        <v>0</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="I75" s="2">
+        <v>0</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="M75" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="N75" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="O75" s="1" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
+      <c r="A76" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="E76" s="2">
+        <v>0</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="I76" s="2">
+        <v>0</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="N76" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
+      <c r="A77" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="E77" s="2">
+        <v>0</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="I77" s="2">
+        <v>0</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="N77" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="O77" s="1" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="A78" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="E78" s="2">
+        <v>0</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="I78" s="2">
+        <v>0</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="N78" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="O78" s="1" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15">
+      <c r="A79" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="E79" s="2">
+        <v>0</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="I79" s="2">
+        <v>0</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="M79" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="N79" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="O79" s="1" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15">
+      <c r="A80" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="E80" s="2">
+        <v>0</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="I80" s="2">
+        <v>0</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="M80" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="N80" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="O80" s="1" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15">
+      <c r="A81" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="E81" s="2">
+        <v>0</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="I81" s="2">
+        <v>0</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="M81" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="N81" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="O81" s="1" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15">
+      <c r="A82" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="E82" s="2">
+        <v>0</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="I82" s="2">
+        <v>0</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M82" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="N82" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="O82" s="1" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15">
+      <c r="A83" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="E83" s="2">
+        <v>0</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="I83" s="2">
+        <v>0</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="N83" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="O83" s="1" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15">
+      <c r="A84" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="E84" s="2">
+        <v>0</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="I84" s="2">
+        <v>0</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="N84" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="O84" s="1" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15">
+      <c r="A85" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="E85" s="2">
+        <v>0</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="I85" s="2">
+        <v>0</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="M85" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="N85" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="O85" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15">
+      <c r="A86" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="E86" s="2">
+        <v>0</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="I86" s="2">
+        <v>0</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="M86" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="N86" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="O86" s="1" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15">
+      <c r="A87" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="E87" s="2">
+        <v>0</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="I87" s="2">
+        <v>0</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="N87" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="O87" s="1" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15">
+      <c r="A88" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="E88" s="2">
+        <v>0</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="I88" s="2">
+        <v>0</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="L88" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="M88" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="N88" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="O88" s="1" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15">
+      <c r="A89" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>940</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="E89" s="2">
+        <v>0</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="I89" s="2">
+        <v>0</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="M89" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="N89" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="O89" s="1" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15">
+      <c r="A90" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>951</v>
+      </c>
+      <c r="E90" s="2">
+        <v>0</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="I90" s="2">
+        <v>0</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="L90" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="M90" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="N90" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="O90" s="1" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15">
+      <c r="A91" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="E91" s="2">
+        <v>0</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="I91" s="2">
+        <v>0</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="M91" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="N91" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="O91" s="1" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15">
+      <c r="A92" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>971</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="E92" s="2">
+        <v>0</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="I92" s="2">
+        <v>0</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="M92" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="N92" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="O92" s="1" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15">
+      <c r="A93" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="E93" s="2">
+        <v>0</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="I93" s="2">
+        <v>0</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="M93" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="N93" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="O93" s="1" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15">
+      <c r="A94" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="E94" s="2">
+        <v>0</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="I94" s="2">
+        <v>0</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="M94" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="N94" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="O94" s="1" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15">
+      <c r="A95" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="E95" s="2">
+        <v>0</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I95" s="2">
+        <v>0</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="M95" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="N95" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="O95" s="1" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15">
+      <c r="A96" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E96" s="2">
+        <v>0</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I96" s="2">
+        <v>0</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L96" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="M96" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="N96" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="O96" s="1" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15">
+      <c r="A97" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="E97" s="2">
+        <v>0</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I97" s="2">
+        <v>0</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="L97" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="M97" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="N97" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="O97" s="1" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15">
+      <c r="A98" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="E98" s="2">
+        <v>0</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="I98" s="2">
+        <v>0</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="M98" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="N98" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="O98" s="1" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15">
+      <c r="A99" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="E99" s="2">
+        <v>0</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="I99" s="2">
+        <v>0</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="M99" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="N99" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="O99" s="1" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15">
+      <c r="A100" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E100" s="2">
+        <v>0</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="I100" s="2">
+        <v>0</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="L100" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="M100" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="N100" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="O100" s="1" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15">
+      <c r="A101" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="E101" s="2">
+        <v>0</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="I101" s="2">
+        <v>0</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="L101" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="M101" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="N101" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="O101" s="1" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15">
+      <c r="A102" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E102" s="2">
+        <v>0</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="I102" s="2">
+        <v>0</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="L102" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="M102" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="N102" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="O102" s="1" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15">
+      <c r="A103" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="E103" s="2">
+        <v>0</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="I103" s="2">
+        <v>0</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="M103" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N103" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="O103" s="1" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15">
+      <c r="A104" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="E104" s="2">
+        <v>0</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="I104" s="2">
+        <v>0</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="L104" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="M104" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="N104" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="O104" s="1" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15">
+      <c r="A105" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E105" s="2">
+        <v>0</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="I105" s="2">
+        <v>0</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="L105" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="M105" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="N105" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="O105" s="1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15">
+      <c r="A106" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="E106" s="2">
+        <v>0</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="I106" s="2">
+        <v>0</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="L106" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="M106" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="N106" s="1" t="s">
+        <v>1124</v>
+      </c>
+      <c r="O106" s="1" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15">
+      <c r="A107" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="E107" s="2">
+        <v>0</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="I107" s="2">
+        <v>0</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="L107" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M107" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="N107" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="O107" s="1" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15">
+      <c r="A108" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E108" s="2">
+        <v>0</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="I108" s="2">
+        <v>0</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="L108" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="M108" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="N108" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="O108" s="1" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15">
+      <c r="A109" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="E109" s="2">
+        <v>0</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="I109" s="2">
+        <v>0</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="L109" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="M109" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="N109" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="O109" s="1" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15">
+      <c r="A110" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="E110" s="2">
+        <v>0</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="I110" s="2">
+        <v>0</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="L110" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="M110" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="N110" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="O110" s="1" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15">
+      <c r="A111" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="E111" s="2">
+        <v>0</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="I111" s="2">
+        <v>0</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>1171</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="L111" s="1" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M111" s="1" t="s">
+        <v>1174</v>
+      </c>
+      <c r="N111" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="O111" s="1" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15">
+      <c r="A112" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="E112" s="2">
+        <v>0</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>1179</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="I112" s="2">
+        <v>0</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="L112" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="M112" s="1" t="s">
+        <v>1183</v>
+      </c>
+      <c r="N112" s="1" t="s">
+        <v>1184</v>
+      </c>
+      <c r="O112" s="1" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15">
+      <c r="A113" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="E113" s="2">
+        <v>0</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="I113" s="2">
+        <v>0</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>1191</v>
+      </c>
+      <c r="K113" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="L113" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="M113" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="N113" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="O113" s="1" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15">
+      <c r="A114" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E114" s="2">
+        <v>0</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>1200</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="I114" s="2">
+        <v>0</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="K114" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="L114" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="M114" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="N114" s="1" t="s">
+        <v>1207</v>
+      </c>
+      <c r="O114" s="1" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15">
+      <c r="A115" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>1211</v>
+      </c>
+      <c r="E115" s="2">
+        <v>0</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="I115" s="2">
+        <v>0</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>1215</v>
+      </c>
+      <c r="K115" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="L115" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="M115" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="N115" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="O115" s="1" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15">
+      <c r="A116" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="E116" s="2">
+        <v>0</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="I116" s="2">
+        <v>0</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>1224</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="L116" s="1" t="s">
+        <v>1226</v>
+      </c>
+      <c r="M116" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="N116" s="1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="O116" s="1" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15">
+      <c r="A117" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E117" s="2">
+        <v>0</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="I117" s="2">
+        <v>0</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="K117" s="1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="L117" s="1" t="s">
+        <v>1236</v>
+      </c>
+      <c r="M117" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="N117" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="O117" s="1" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15">
+      <c r="A118" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E118" s="2">
+        <v>0</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>1243</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>1244</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="I118" s="2">
+        <v>0</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="L118" s="1" t="s">
+        <v>1248</v>
+      </c>
+      <c r="M118" s="1" t="s">
+        <v>1249</v>
+      </c>
+      <c r="N118" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="O118" s="1" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15">
+      <c r="A119" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="E119" s="2">
+        <v>0</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="I119" s="2">
+        <v>0</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="K119" s="1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="L119" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="M119" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="N119" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="O119" s="1" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15">
+      <c r="A120" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="E120" s="2">
+        <v>0</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>1263</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I120" s="2">
+        <v>0</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="K120" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="L120" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="M120" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="N120" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="O120" s="1" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15">
+      <c r="A121" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E121" s="2">
+        <v>0</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="I121" s="2">
+        <v>0</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="L121" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="M121" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="N121" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="O121" s="1" t="s">
+        <v>1283</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/mainWidget/mainWidget/src/database/计算模型-快速烤燃试验.xlsx
+++ b/mainWidget/mainWidget/src/database/计算模型-快速烤燃试验.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28F7B325-4BA8-4DEB-9326-5CC66CEEDAE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="22155" windowHeight="13320"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -184,9 +178,6 @@
     <t>L (mm)</t>
   </si>
   <si>
-    <t>M (mm)</t>
-  </si>
-  <si>
     <t>22.4016-0.0067*B+0.0000*C-0.1051*D-0.0481*E-0.0103*F+0.0000*G-0.9756*H-0.0278*I+0.0057*J-0.0372*K-5.3699*L+1.0405*M</t>
   </si>
   <si>
@@ -4415,13 +4406,35 @@
   </si>
   <si>
     <t>120</t>
+  </si>
+  <si>
+    <r>
+      <t>M (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>℃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -4443,6 +4456,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -4480,7 +4499,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{1C87F38B-8B09-47E1-A0A6-D5B12A61D915}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -4496,9 +4515,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4536,7 +4555,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4608,7 +4627,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4781,12 +4800,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O121"/>
-  <sheetFormatPr defaultRowHeight="14.6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="18.53515625" customWidth="1"/>
-    <col min="3" max="15" width="9.23046875" style="2"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="15" width="9.28515625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -4832,8 +4851,8 @@
       <c r="N1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>54</v>
+      <c r="O1" s="3" t="s">
+        <v>1363</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -4841,46 +4860,46 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E2" s="2">
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I2" s="2">
         <v>0</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -4888,46 +4907,46 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E3" s="2">
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I3" s="2">
         <v>0</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -4935,46 +4954,46 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E4" s="2">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I4" s="2">
         <v>0</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -4982,46 +5001,46 @@
         <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E5" s="2">
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I5" s="2">
         <v>0</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -5029,46 +5048,46 @@
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E6" s="2">
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I6" s="2">
         <v>0</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -5076,46 +5095,46 @@
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E7" s="2">
         <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I7" s="2">
         <v>0</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -5123,46 +5142,46 @@
         <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I8" s="2">
         <v>0</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -5170,46 +5189,46 @@
         <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E9" s="2">
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I9" s="2">
         <v>0</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -5217,46 +5236,46 @@
         <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E10" s="2">
         <v>0</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I10" s="2">
         <v>0</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -5264,46 +5283,46 @@
         <v>12</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E11" s="2">
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I11" s="2">
         <v>0</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -5311,46 +5330,46 @@
         <v>13</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E12" s="2">
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I12" s="2">
         <v>0</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -5358,46 +5377,46 @@
         <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I13" s="2">
         <v>0</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -5405,46 +5424,46 @@
         <v>15</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I14" s="2">
         <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L14" s="2">
         <v>3.4200000000000001E-2</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -5452,46 +5471,46 @@
         <v>16</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E15" s="2">
         <v>0</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I15" s="2">
         <v>0</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -5499,46 +5518,46 @@
         <v>17</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E16" s="2">
         <v>0</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I16" s="2">
         <v>0</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -5546,46 +5565,46 @@
         <v>18</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E17" s="2">
         <v>0</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I17" s="2">
         <v>0</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="18" spans="1:15">
@@ -5593,46 +5612,46 @@
         <v>19</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E18" s="2">
         <v>0</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I18" s="2">
         <v>0</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" spans="1:15">
@@ -5640,46 +5659,46 @@
         <v>20</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E19" s="2">
         <v>0</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I19" s="2">
         <v>0</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="20" spans="1:15">
@@ -5687,46 +5706,46 @@
         <v>21</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E20" s="2">
         <v>0</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I20" s="2">
         <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="21" spans="1:15">
@@ -5734,46 +5753,46 @@
         <v>22</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E21" s="2">
         <v>0</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I21" s="2">
         <v>0</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -5781,46 +5800,46 @@
         <v>23</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I22" s="2">
         <v>0</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="23" spans="1:15">
@@ -5828,46 +5847,46 @@
         <v>24</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E23" s="2">
         <v>0</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I23" s="2">
         <v>0</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="24" spans="1:15">
@@ -5875,46 +5894,46 @@
         <v>25</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E24" s="2">
         <v>0</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I24" s="2">
         <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="25" spans="1:15">
@@ -5922,46 +5941,46 @@
         <v>26</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E25" s="2">
         <v>0</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I25" s="2">
         <v>0</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="26" spans="1:15">
@@ -5969,46 +5988,46 @@
         <v>27</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E26" s="2">
         <v>0</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I26" s="2">
         <v>0</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="27" spans="1:15">
@@ -6016,46 +6035,46 @@
         <v>28</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E27" s="2">
         <v>0</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I27" s="2">
         <v>0</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="28" spans="1:15">
@@ -6063,46 +6082,46 @@
         <v>29</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E28" s="2">
         <v>0</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I28" s="2">
         <v>0</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="29" spans="1:15">
@@ -6110,46 +6129,46 @@
         <v>30</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E29" s="2">
         <v>0</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I29" s="2">
         <v>0</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="30" spans="1:15">
@@ -6157,46 +6176,46 @@
         <v>31</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E30" s="2">
         <v>0</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I30" s="2">
         <v>0</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="31" spans="1:15">
@@ -6204,46 +6223,46 @@
         <v>32</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E31" s="2">
         <v>0</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I31" s="2">
         <v>0</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="32" spans="1:15">
@@ -6251,46 +6270,46 @@
         <v>33</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E32" s="2">
         <v>0</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I32" s="2">
         <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="33" spans="1:15">
@@ -6298,46 +6317,46 @@
         <v>34</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E33" s="2">
         <v>0</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I33" s="2">
         <v>0</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="34" spans="1:15">
@@ -6345,46 +6364,46 @@
         <v>35</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E34" s="2">
         <v>0</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I34" s="2">
         <v>0</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="35" spans="1:15">
@@ -6392,46 +6411,46 @@
         <v>36</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E35" s="2">
         <v>0</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I35" s="2">
         <v>0</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="36" spans="1:15">
@@ -6439,46 +6458,46 @@
         <v>37</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E36" s="2">
         <v>0</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I36" s="2">
         <v>0</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="37" spans="1:15">
@@ -6486,46 +6505,46 @@
         <v>38</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E37" s="2">
         <v>0</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I37" s="2">
         <v>0</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="38" spans="1:15">
@@ -6533,46 +6552,46 @@
         <v>39</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E38" s="2">
         <v>0</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I38" s="2">
         <v>0</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="39" spans="1:15">
@@ -6580,46 +6599,46 @@
         <v>40</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E39" s="2">
         <v>0</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I39" s="2">
         <v>0</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="40" spans="1:15">
@@ -6627,46 +6646,46 @@
         <v>41</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E40" s="2">
         <v>0</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I40" s="2">
         <v>0</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="41" spans="1:15">
@@ -6674,3810 +6693,3811 @@
         <v>42</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="E41" s="2">
         <v>0</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I41" s="2">
         <v>0</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="M41" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="N41" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>329</v>
-      </c>
       <c r="O41" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="42" spans="1:15">
       <c r="A42" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="E42" s="2">
+        <v>0</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="E42" s="2">
-        <v>0</v>
-      </c>
-      <c r="F42" s="1" t="s">
+      <c r="G42" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="H42" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="I42" s="2">
+        <v>0</v>
+      </c>
+      <c r="J42" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="I42" s="2">
-        <v>0</v>
-      </c>
-      <c r="J42" s="1" t="s">
+      <c r="K42" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="K42" s="1" t="s">
+      <c r="L42" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="L42" s="1" t="s">
+      <c r="M42" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="M42" s="1" t="s">
+      <c r="N42" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="N42" s="1" t="s">
+      <c r="O42" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="O42" s="1" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="43" spans="1:15">
       <c r="A43" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="D43" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="E43" s="2">
+        <v>0</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="E43" s="2">
-        <v>0</v>
-      </c>
-      <c r="F43" s="1" t="s">
+      <c r="G43" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="H43" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="I43" s="2">
+        <v>0</v>
+      </c>
+      <c r="J43" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="I43" s="2">
-        <v>0</v>
-      </c>
-      <c r="J43" s="1" t="s">
+      <c r="K43" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="K43" s="1" t="s">
+      <c r="L43" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="L43" s="1" t="s">
+      <c r="M43" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="M43" s="1" t="s">
+      <c r="N43" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="N43" s="1" t="s">
+      <c r="O43" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="44" spans="1:15">
       <c r="A44" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="D44" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="E44" s="2">
+        <v>0</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="E44" s="2">
-        <v>0</v>
-      </c>
-      <c r="F44" s="1" t="s">
+      <c r="G44" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="H44" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="I44" s="2">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="I44" s="2">
-        <v>0</v>
-      </c>
-      <c r="J44" s="1" t="s">
+      <c r="K44" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="K44" s="1" t="s">
+      <c r="L44" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="L44" s="1" t="s">
+      <c r="M44" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="M44" s="1" t="s">
+      <c r="N44" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="N44" s="1" t="s">
+      <c r="O44" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="O44" s="1" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="45" spans="1:15">
       <c r="A45" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D45" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="D45" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="E45" s="2">
-        <v>0</v>
-      </c>
-      <c r="F45" s="1" t="s">
+      <c r="G45" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="H45" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="I45" s="2">
+        <v>0</v>
+      </c>
+      <c r="J45" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="I45" s="2">
-        <v>0</v>
-      </c>
-      <c r="J45" s="1" t="s">
+      <c r="K45" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="K45" s="1" t="s">
+      <c r="L45" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="L45" s="1" t="s">
+      <c r="M45" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="M45" s="1" t="s">
+      <c r="N45" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="N45" s="1" t="s">
+      <c r="O45" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="O45" s="1" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="46" spans="1:15">
       <c r="A46" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="E46" s="2">
+        <v>0</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="E46" s="2">
-        <v>0</v>
-      </c>
-      <c r="F46" s="1" t="s">
+      <c r="G46" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="H46" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="I46" s="2">
+        <v>0</v>
+      </c>
+      <c r="J46" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="I46" s="2">
-        <v>0</v>
-      </c>
-      <c r="J46" s="1" t="s">
+      <c r="K46" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="K46" s="1" t="s">
+      <c r="L46" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="L46" s="1" t="s">
+      <c r="M46" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="M46" s="1" t="s">
+      <c r="N46" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="N46" s="1" t="s">
+      <c r="O46" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="O46" s="1" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="47" spans="1:15">
       <c r="A47" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="D47" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="E47" s="2">
+        <v>0</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="E47" s="2">
-        <v>0</v>
-      </c>
-      <c r="F47" s="1" t="s">
+      <c r="G47" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="H47" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="I47" s="2">
+        <v>0</v>
+      </c>
+      <c r="J47" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="I47" s="2">
-        <v>0</v>
-      </c>
-      <c r="J47" s="1" t="s">
+      <c r="K47" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="K47" s="1" t="s">
+      <c r="L47" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="L47" s="1" t="s">
+      <c r="M47" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="M47" s="1" t="s">
+      <c r="N47" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="N47" s="1" t="s">
+      <c r="O47" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="O47" s="1" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="48" spans="1:15">
       <c r="A48" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="E48" s="2">
+        <v>0</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="E48" s="2">
-        <v>0</v>
-      </c>
-      <c r="F48" s="1" t="s">
+      <c r="G48" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="H48" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="I48" s="2">
+        <v>0</v>
+      </c>
+      <c r="J48" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="H48" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="I48" s="2">
-        <v>0</v>
-      </c>
-      <c r="J48" s="1" t="s">
+      <c r="K48" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="K48" s="1" t="s">
+      <c r="L48" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="L48" s="1" t="s">
+      <c r="M48" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="M48" s="1" t="s">
+      <c r="N48" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="N48" s="1" t="s">
+      <c r="O48" s="1" t="s">
         <v>476</v>
-      </c>
-      <c r="O48" s="1" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="49" spans="1:15">
       <c r="A49" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="D49" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="E49" s="2">
+        <v>0</v>
+      </c>
+      <c r="F49" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="E49" s="2">
-        <v>0</v>
-      </c>
-      <c r="F49" s="1" t="s">
+      <c r="G49" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="H49" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="I49" s="2">
+        <v>0</v>
+      </c>
+      <c r="J49" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="I49" s="2">
-        <v>0</v>
-      </c>
-      <c r="J49" s="1" t="s">
+      <c r="K49" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="L49" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="L49" s="1" t="s">
+      <c r="M49" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="M49" s="1" t="s">
+      <c r="N49" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="N49" s="1" t="s">
+      <c r="O49" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="O49" s="1" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="50" spans="1:15">
       <c r="A50" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="E50" s="2">
+        <v>0</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="E50" s="2">
-        <v>0</v>
-      </c>
-      <c r="F50" s="1" t="s">
+      <c r="G50" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="H50" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="I50" s="2">
+        <v>0</v>
+      </c>
+      <c r="J50" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="I50" s="2">
-        <v>0</v>
-      </c>
-      <c r="J50" s="1" t="s">
+      <c r="K50" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="K50" s="1" t="s">
+      <c r="L50" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="L50" s="1" t="s">
+      <c r="M50" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="M50" s="1" t="s">
+      <c r="N50" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="N50" s="1" t="s">
+      <c r="O50" s="1" t="s">
         <v>500</v>
-      </c>
-      <c r="O50" s="1" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="51" spans="1:15">
       <c r="A51" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="E51" s="2">
+        <v>0</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="E51" s="2">
-        <v>0</v>
-      </c>
-      <c r="F51" s="1" t="s">
+      <c r="G51" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="H51" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="I51" s="2">
+        <v>0</v>
+      </c>
+      <c r="J51" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="I51" s="2">
-        <v>0</v>
-      </c>
-      <c r="J51" s="1" t="s">
+      <c r="K51" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="K51" s="1" t="s">
+      <c r="L51" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="M51" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="L51" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="M51" s="1" t="s">
+      <c r="N51" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="N51" s="1" t="s">
+      <c r="O51" s="1" t="s">
         <v>511</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="52" spans="1:15">
       <c r="A52" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="E52" s="2">
+        <v>0</v>
+      </c>
+      <c r="F52" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="E52" s="2">
-        <v>0</v>
-      </c>
-      <c r="F52" s="1" t="s">
+      <c r="G52" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="H52" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="H52" s="1" t="s">
+      <c r="I52" s="2">
+        <v>0</v>
+      </c>
+      <c r="J52" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="I52" s="2">
-        <v>0</v>
-      </c>
-      <c r="J52" s="1" t="s">
+      <c r="K52" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="K52" s="1" t="s">
+      <c r="L52" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="L52" s="1" t="s">
+      <c r="M52" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="M52" s="1" t="s">
+      <c r="N52" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="N52" s="1" t="s">
+      <c r="O52" s="1" t="s">
         <v>523</v>
-      </c>
-      <c r="O52" s="1" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="53" spans="1:15">
       <c r="A53" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="E53" s="2">
+        <v>0</v>
+      </c>
+      <c r="F53" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="E53" s="2">
-        <v>0</v>
-      </c>
-      <c r="F53" s="1" t="s">
+      <c r="G53" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="H53" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="I53" s="2">
+        <v>0</v>
+      </c>
+      <c r="J53" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="I53" s="2">
-        <v>0</v>
-      </c>
-      <c r="J53" s="1" t="s">
+      <c r="K53" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="K53" s="1" t="s">
+      <c r="L53" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="L53" s="1" t="s">
+      <c r="M53" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="M53" s="1" t="s">
+      <c r="N53" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="N53" s="1" t="s">
+      <c r="O53" s="1" t="s">
         <v>535</v>
-      </c>
-      <c r="O53" s="1" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="54" spans="1:15">
       <c r="A54" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="D54" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="E54" s="2">
+        <v>0</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="E54" s="2">
-        <v>0</v>
-      </c>
-      <c r="F54" s="1" t="s">
+      <c r="G54" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="H54" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="I54" s="2">
+        <v>0</v>
+      </c>
+      <c r="J54" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="H54" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="I54" s="2">
-        <v>0</v>
-      </c>
-      <c r="J54" s="1" t="s">
+      <c r="K54" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="K54" s="1" t="s">
+      <c r="L54" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="L54" s="1" t="s">
+      <c r="M54" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="M54" s="1" t="s">
+      <c r="N54" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="N54" s="1" t="s">
+      <c r="O54" s="1" t="s">
         <v>546</v>
-      </c>
-      <c r="O54" s="1" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="55" spans="1:15">
       <c r="A55" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="E55" s="2">
+        <v>0</v>
+      </c>
+      <c r="F55" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="E55" s="2">
-        <v>0</v>
-      </c>
-      <c r="F55" s="1" t="s">
+      <c r="G55" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="H55" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="H55" s="1" t="s">
+      <c r="I55" s="2">
+        <v>0</v>
+      </c>
+      <c r="J55" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="I55" s="2">
-        <v>0</v>
-      </c>
-      <c r="J55" s="1" t="s">
+      <c r="K55" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="K55" s="1" t="s">
+      <c r="L55" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="L55" s="1" t="s">
+      <c r="M55" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="M55" s="1" t="s">
+      <c r="N55" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="N55" s="1" t="s">
+      <c r="O55" s="1" t="s">
         <v>558</v>
-      </c>
-      <c r="O55" s="1" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="56" spans="1:15">
       <c r="A56" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="D56" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="E56" s="2">
+        <v>0</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="E56" s="2">
-        <v>0</v>
-      </c>
-      <c r="F56" s="1" t="s">
+      <c r="G56" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="G56" s="1" t="s">
+      <c r="H56" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="H56" s="1" t="s">
+      <c r="I56" s="2">
+        <v>0</v>
+      </c>
+      <c r="J56" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="I56" s="2">
-        <v>0</v>
-      </c>
-      <c r="J56" s="1" t="s">
+      <c r="K56" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="K56" s="1" t="s">
+      <c r="L56" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="L56" s="1" t="s">
+      <c r="M56" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="M56" s="1" t="s">
+      <c r="N56" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="N56" s="1" t="s">
+      <c r="O56" s="1" t="s">
         <v>570</v>
-      </c>
-      <c r="O56" s="1" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="57" spans="1:15">
       <c r="A57" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="D57" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="E57" s="2">
+        <v>0</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="E57" s="2">
-        <v>0</v>
-      </c>
-      <c r="F57" s="1" t="s">
+      <c r="G57" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="H57" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="G57" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="H57" s="1" t="s">
+      <c r="I57" s="2">
+        <v>0</v>
+      </c>
+      <c r="J57" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="I57" s="2">
-        <v>0</v>
-      </c>
-      <c r="J57" s="1" t="s">
+      <c r="K57" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="K57" s="1" t="s">
+      <c r="L57" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="L57" s="1" t="s">
+      <c r="M57" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="M57" s="1" t="s">
+      <c r="N57" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="N57" s="1" t="s">
+      <c r="O57" s="1" t="s">
         <v>581</v>
-      </c>
-      <c r="O57" s="1" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="58" spans="1:15">
       <c r="A58" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="D58" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="E58" s="2">
+        <v>0</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="E58" s="2">
-        <v>0</v>
-      </c>
-      <c r="F58" s="1" t="s">
+      <c r="G58" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="G58" s="1" t="s">
+      <c r="H58" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="H58" s="1" t="s">
+      <c r="I58" s="2">
+        <v>0</v>
+      </c>
+      <c r="J58" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="I58" s="2">
-        <v>0</v>
-      </c>
-      <c r="J58" s="1" t="s">
+      <c r="K58" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="K58" s="1" t="s">
+      <c r="L58" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="L58" s="1" t="s">
+      <c r="M58" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="M58" s="1" t="s">
+      <c r="N58" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="N58" s="1" t="s">
+      <c r="O58" s="1" t="s">
         <v>593</v>
-      </c>
-      <c r="O58" s="1" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="59" spans="1:15">
       <c r="A59" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="D59" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="E59" s="2">
+        <v>0</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="E59" s="2">
-        <v>0</v>
-      </c>
-      <c r="F59" s="1" t="s">
+      <c r="G59" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="G59" s="1" t="s">
+      <c r="H59" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="H59" s="1" t="s">
+      <c r="I59" s="2">
+        <v>0</v>
+      </c>
+      <c r="J59" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="I59" s="2">
-        <v>0</v>
-      </c>
-      <c r="J59" s="1" t="s">
+      <c r="K59" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="K59" s="1" t="s">
+      <c r="L59" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="L59" s="1" t="s">
+      <c r="M59" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="M59" s="1" t="s">
+      <c r="N59" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="N59" s="1" t="s">
+      <c r="O59" s="1" t="s">
         <v>605</v>
-      </c>
-      <c r="O59" s="1" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="60" spans="1:15">
       <c r="A60" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="D60" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="E60" s="2">
+        <v>0</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="E60" s="2">
-        <v>0</v>
-      </c>
-      <c r="F60" s="1" t="s">
+      <c r="G60" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="G60" s="1" t="s">
+      <c r="H60" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="H60" s="1" t="s">
+      <c r="I60" s="2">
+        <v>0</v>
+      </c>
+      <c r="J60" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="I60" s="2">
-        <v>0</v>
-      </c>
-      <c r="J60" s="1" t="s">
+      <c r="K60" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="L60" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="K60" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="L60" s="1" t="s">
+      <c r="M60" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="M60" s="1" t="s">
+      <c r="N60" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="N60" s="1" t="s">
+      <c r="O60" s="1" t="s">
         <v>616</v>
-      </c>
-      <c r="O60" s="1" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="61" spans="1:15">
       <c r="A61" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>618</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="D61" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E61" s="2">
+        <v>0</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="E61" s="2">
-        <v>0</v>
-      </c>
-      <c r="F61" s="1" t="s">
+      <c r="G61" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="G61" s="1" t="s">
+      <c r="H61" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="H61" s="1" t="s">
+      <c r="I61" s="2">
+        <v>0</v>
+      </c>
+      <c r="J61" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="I61" s="2">
-        <v>0</v>
-      </c>
-      <c r="J61" s="1" t="s">
+      <c r="K61" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="K61" s="1" t="s">
+      <c r="L61" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="L61" s="1" t="s">
+      <c r="M61" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="M61" s="1" t="s">
+      <c r="N61" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="N61" s="1" t="s">
+      <c r="O61" s="1" t="s">
         <v>627</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="62" spans="1:15">
       <c r="A62" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="D62" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="E62" s="2">
+        <v>0</v>
+      </c>
+      <c r="F62" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="E62" s="2">
-        <v>0</v>
-      </c>
-      <c r="F62" s="1" t="s">
+      <c r="G62" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="G62" s="1" t="s">
+      <c r="H62" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="H62" s="1" t="s">
+      <c r="I62" s="2">
+        <v>0</v>
+      </c>
+      <c r="J62" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="I62" s="2">
-        <v>0</v>
-      </c>
-      <c r="J62" s="1" t="s">
+      <c r="K62" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="K62" s="1" t="s">
+      <c r="L62" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="L62" s="1" t="s">
+      <c r="M62" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="M62" s="1" t="s">
+      <c r="N62" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="N62" s="1" t="s">
+      <c r="O62" s="1" t="s">
         <v>639</v>
-      </c>
-      <c r="O62" s="1" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="63" spans="1:15">
       <c r="A63" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="D63" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="E63" s="2">
+        <v>0</v>
+      </c>
+      <c r="F63" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="E63" s="2">
-        <v>0</v>
-      </c>
-      <c r="F63" s="1" t="s">
+      <c r="G63" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="G63" s="1" t="s">
+      <c r="H63" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="I63" s="2">
+        <v>0</v>
+      </c>
+      <c r="J63" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="H63" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="I63" s="2">
-        <v>0</v>
-      </c>
-      <c r="J63" s="1" t="s">
+      <c r="K63" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="K63" s="1" t="s">
+      <c r="L63" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="L63" s="1" t="s">
+      <c r="M63" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="M63" s="1" t="s">
+      <c r="N63" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="N63" s="1" t="s">
+      <c r="O63" s="1" t="s">
         <v>650</v>
-      </c>
-      <c r="O63" s="1" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="64" spans="1:15">
       <c r="A64" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="E64" s="2">
+        <v>0</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="E64" s="2">
-        <v>0</v>
-      </c>
-      <c r="F64" s="1" t="s">
+      <c r="G64" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="G64" s="1" t="s">
+      <c r="H64" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="H64" s="1" t="s">
+      <c r="I64" s="2">
+        <v>0</v>
+      </c>
+      <c r="J64" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="I64" s="2">
-        <v>0</v>
-      </c>
-      <c r="J64" s="1" t="s">
+      <c r="K64" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="K64" s="1" t="s">
+      <c r="L64" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="L64" s="1" t="s">
+      <c r="M64" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="M64" s="1" t="s">
+      <c r="N64" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="N64" s="1" t="s">
+      <c r="O64" s="1" t="s">
         <v>662</v>
-      </c>
-      <c r="O64" s="1" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="65" spans="1:15">
       <c r="A65" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="D65" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="E65" s="2">
+        <v>0</v>
+      </c>
+      <c r="F65" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="E65" s="2">
-        <v>0</v>
-      </c>
-      <c r="F65" s="1" t="s">
+      <c r="G65" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="G65" s="1" t="s">
+      <c r="H65" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="H65" s="1" t="s">
+      <c r="I65" s="2">
+        <v>0</v>
+      </c>
+      <c r="J65" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="I65" s="2">
-        <v>0</v>
-      </c>
-      <c r="J65" s="1" t="s">
+      <c r="K65" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="K65" s="1" t="s">
+      <c r="L65" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="L65" s="1" t="s">
+      <c r="M65" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="M65" s="1" t="s">
+      <c r="N65" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="N65" s="1" t="s">
+      <c r="O65" s="1" t="s">
         <v>674</v>
-      </c>
-      <c r="O65" s="1" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="66" spans="1:15">
       <c r="A66" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="B66" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="D66" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="E66" s="2">
+        <v>0</v>
+      </c>
+      <c r="F66" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="E66" s="2">
-        <v>0</v>
-      </c>
-      <c r="F66" s="1" t="s">
+      <c r="G66" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="G66" s="1" t="s">
+      <c r="H66" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="H66" s="1" t="s">
+      <c r="I66" s="2">
+        <v>0</v>
+      </c>
+      <c r="J66" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="I66" s="2">
-        <v>0</v>
-      </c>
-      <c r="J66" s="1" t="s">
+      <c r="K66" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="K66" s="1" t="s">
+      <c r="L66" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="L66" s="1" t="s">
+      <c r="M66" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="M66" s="1" t="s">
+      <c r="N66" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="N66" s="1" t="s">
+      <c r="O66" s="1" t="s">
         <v>686</v>
-      </c>
-      <c r="O66" s="1" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="67" spans="1:15">
       <c r="A67" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="D67" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="E67" s="2">
+        <v>0</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="E67" s="2">
-        <v>0</v>
-      </c>
-      <c r="F67" s="1" t="s">
+      <c r="G67" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="G67" s="1" t="s">
+      <c r="H67" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="H67" s="1" t="s">
+      <c r="I67" s="2">
+        <v>0</v>
+      </c>
+      <c r="J67" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="I67" s="2">
-        <v>0</v>
-      </c>
-      <c r="J67" s="1" t="s">
+      <c r="K67" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="K67" s="1" t="s">
+      <c r="L67" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="L67" s="1" t="s">
+      <c r="M67" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="M67" s="1" t="s">
+      <c r="N67" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="N67" s="1" t="s">
+      <c r="O67" s="1" t="s">
         <v>697</v>
-      </c>
-      <c r="O67" s="1" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="68" spans="1:15">
       <c r="A68" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="D68" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="E68" s="2">
+        <v>0</v>
+      </c>
+      <c r="F68" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="E68" s="2">
-        <v>0</v>
-      </c>
-      <c r="F68" s="1" t="s">
+      <c r="G68" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="G68" s="1" t="s">
+      <c r="H68" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="H68" s="1" t="s">
+      <c r="I68" s="2">
+        <v>0</v>
+      </c>
+      <c r="J68" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="I68" s="2">
-        <v>0</v>
-      </c>
-      <c r="J68" s="1" t="s">
+      <c r="K68" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="K68" s="1" t="s">
+      <c r="L68" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="L68" s="1" t="s">
+      <c r="M68" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="M68" s="1" t="s">
+      <c r="N68" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="N68" s="1" t="s">
+      <c r="O68" s="1" t="s">
         <v>709</v>
-      </c>
-      <c r="O68" s="1" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="69" spans="1:15">
       <c r="A69" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="D69" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="E69" s="2">
+        <v>0</v>
+      </c>
+      <c r="F69" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="E69" s="2">
-        <v>0</v>
-      </c>
-      <c r="F69" s="1" t="s">
+      <c r="G69" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="G69" s="1" t="s">
+      <c r="H69" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="H69" s="1" t="s">
+      <c r="I69" s="2">
+        <v>0</v>
+      </c>
+      <c r="J69" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="I69" s="2">
-        <v>0</v>
-      </c>
-      <c r="J69" s="1" t="s">
+      <c r="K69" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="K69" s="1" t="s">
+      <c r="L69" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="L69" s="1" t="s">
+      <c r="M69" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="M69" s="1" t="s">
+      <c r="N69" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="N69" s="1" t="s">
+      <c r="O69" s="1" t="s">
         <v>721</v>
-      </c>
-      <c r="O69" s="1" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="70" spans="1:15">
       <c r="A70" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="D70" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="E70" s="2">
+        <v>0</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="E70" s="2">
-        <v>0</v>
-      </c>
-      <c r="F70" s="1" t="s">
+      <c r="G70" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="G70" s="1" t="s">
+      <c r="H70" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="H70" s="1" t="s">
+      <c r="I70" s="2">
+        <v>0</v>
+      </c>
+      <c r="J70" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="I70" s="2">
-        <v>0</v>
-      </c>
-      <c r="J70" s="1" t="s">
+      <c r="K70" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="K70" s="1" t="s">
+      <c r="L70" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="L70" s="1" t="s">
+      <c r="M70" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="M70" s="1" t="s">
+      <c r="N70" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="N70" s="1" t="s">
+      <c r="O70" s="1" t="s">
         <v>733</v>
-      </c>
-      <c r="O70" s="1" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="71" spans="1:15">
       <c r="A71" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="B71" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="D71" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="E71" s="2">
+        <v>0</v>
+      </c>
+      <c r="F71" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="E71" s="2">
-        <v>0</v>
-      </c>
-      <c r="F71" s="1" t="s">
+      <c r="G71" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="G71" s="1" t="s">
+      <c r="H71" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="H71" s="1" t="s">
+      <c r="I71" s="2">
+        <v>0</v>
+      </c>
+      <c r="J71" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="I71" s="2">
-        <v>0</v>
-      </c>
-      <c r="J71" s="1" t="s">
+      <c r="K71" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="K71" s="1" t="s">
+      <c r="L71" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="L71" s="1" t="s">
+      <c r="M71" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="M71" s="1" t="s">
+      <c r="N71" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="N71" s="1" t="s">
+      <c r="O71" s="1" t="s">
         <v>745</v>
-      </c>
-      <c r="O71" s="1" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="72" spans="1:15">
       <c r="A72" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="B72" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="D72" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="E72" s="2">
+        <v>0</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="E72" s="2">
-        <v>0</v>
-      </c>
-      <c r="F72" s="1" t="s">
+      <c r="G72" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="G72" s="1" t="s">
+      <c r="H72" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="H72" s="1" t="s">
+      <c r="I72" s="2">
+        <v>0</v>
+      </c>
+      <c r="J72" s="1" t="s">
         <v>752</v>
       </c>
-      <c r="I72" s="2">
-        <v>0</v>
-      </c>
-      <c r="J72" s="1" t="s">
+      <c r="K72" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="K72" s="1" t="s">
+      <c r="L72" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="L72" s="1" t="s">
+      <c r="M72" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="M72" s="1" t="s">
+      <c r="N72" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="N72" s="1" t="s">
+      <c r="O72" s="1" t="s">
         <v>757</v>
-      </c>
-      <c r="O72" s="1" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="73" spans="1:15">
       <c r="A73" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="B73" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="D73" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="E73" s="2">
+        <v>0</v>
+      </c>
+      <c r="F73" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="E73" s="2">
-        <v>0</v>
-      </c>
-      <c r="F73" s="1" t="s">
+      <c r="G73" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="G73" s="1" t="s">
+      <c r="H73" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="I73" s="2">
+        <v>0</v>
+      </c>
+      <c r="J73" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="I73" s="2">
-        <v>0</v>
-      </c>
-      <c r="J73" s="1" t="s">
+      <c r="K73" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="K73" s="1" t="s">
+      <c r="L73" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="L73" s="1" t="s">
+      <c r="M73" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="M73" s="1" t="s">
+      <c r="N73" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="N73" s="1" t="s">
+      <c r="O73" s="1" t="s">
         <v>769</v>
-      </c>
-      <c r="O73" s="1" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="74" spans="1:15">
       <c r="A74" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="B74" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="D74" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="E74" s="2">
+        <v>0</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="E74" s="2">
-        <v>0</v>
-      </c>
-      <c r="F74" s="1" t="s">
+      <c r="G74" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="G74" s="1" t="s">
+      <c r="H74" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="H74" s="1" t="s">
+      <c r="I74" s="2">
+        <v>0</v>
+      </c>
+      <c r="J74" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="I74" s="2">
-        <v>0</v>
-      </c>
-      <c r="J74" s="1" t="s">
+      <c r="K74" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="K74" s="1" t="s">
+      <c r="L74" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="L74" s="1" t="s">
+      <c r="M74" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="M74" s="1" t="s">
+      <c r="N74" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="N74" s="1" t="s">
+      <c r="O74" s="1" t="s">
         <v>781</v>
-      </c>
-      <c r="O74" s="1" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="75" spans="1:15">
       <c r="A75" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="B75" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="D75" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="E75" s="2">
+        <v>0</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="E75" s="2">
-        <v>0</v>
-      </c>
-      <c r="F75" s="1" t="s">
+      <c r="G75" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="H75" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="G75" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="H75" s="1" t="s">
+      <c r="I75" s="2">
+        <v>0</v>
+      </c>
+      <c r="J75" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="I75" s="2">
-        <v>0</v>
-      </c>
-      <c r="J75" s="1" t="s">
+      <c r="K75" s="1" t="s">
         <v>788</v>
       </c>
-      <c r="K75" s="1" t="s">
+      <c r="L75" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="L75" s="1" t="s">
+      <c r="M75" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="M75" s="1" t="s">
+      <c r="N75" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="N75" s="1" t="s">
+      <c r="O75" s="1" t="s">
         <v>792</v>
-      </c>
-      <c r="O75" s="1" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="76" spans="1:15">
       <c r="A76" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="D76" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="E76" s="2">
+        <v>0</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="E76" s="2">
-        <v>0</v>
-      </c>
-      <c r="F76" s="1" t="s">
+      <c r="G76" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="G76" s="1" t="s">
+      <c r="H76" s="1" t="s">
         <v>798</v>
       </c>
-      <c r="H76" s="1" t="s">
+      <c r="I76" s="2">
+        <v>0</v>
+      </c>
+      <c r="J76" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="I76" s="2">
-        <v>0</v>
-      </c>
-      <c r="J76" s="1" t="s">
+      <c r="K76" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="K76" s="1" t="s">
+      <c r="L76" s="1" t="s">
         <v>801</v>
       </c>
-      <c r="L76" s="1" t="s">
+      <c r="M76" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="M76" s="1" t="s">
+      <c r="N76" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="N76" s="1" t="s">
+      <c r="O76" s="1" t="s">
         <v>804</v>
-      </c>
-      <c r="O76" s="1" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="77" spans="1:15">
       <c r="A77" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="B77" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="D77" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="E77" s="2">
+        <v>0</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="E77" s="2">
-        <v>0</v>
-      </c>
-      <c r="F77" s="1" t="s">
+      <c r="G77" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="H77" s="1" t="s">
         <v>809</v>
       </c>
-      <c r="G77" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="H77" s="1" t="s">
+      <c r="I77" s="2">
+        <v>0</v>
+      </c>
+      <c r="J77" s="1" t="s">
         <v>810</v>
       </c>
-      <c r="I77" s="2">
-        <v>0</v>
-      </c>
-      <c r="J77" s="1" t="s">
+      <c r="K77" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="K77" s="1" t="s">
+      <c r="L77" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="M77" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="L77" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="M77" s="1" t="s">
+      <c r="N77" s="1" t="s">
         <v>813</v>
       </c>
-      <c r="N77" s="1" t="s">
+      <c r="O77" s="1" t="s">
         <v>814</v>
-      </c>
-      <c r="O77" s="1" t="s">
-        <v>815</v>
       </c>
     </row>
     <row r="78" spans="1:15">
       <c r="A78" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="B78" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>816</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="D78" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="E78" s="2">
+        <v>0</v>
+      </c>
+      <c r="F78" s="1" t="s">
         <v>817</v>
       </c>
-      <c r="D78" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="E78" s="2">
-        <v>0</v>
-      </c>
-      <c r="F78" s="1" t="s">
+      <c r="G78" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="G78" s="1" t="s">
+      <c r="H78" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="H78" s="1" t="s">
+      <c r="I78" s="2">
+        <v>0</v>
+      </c>
+      <c r="J78" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="I78" s="2">
-        <v>0</v>
-      </c>
-      <c r="J78" s="1" t="s">
+      <c r="K78" s="1" t="s">
         <v>821</v>
       </c>
-      <c r="K78" s="1" t="s">
+      <c r="L78" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="L78" s="1" t="s">
+      <c r="M78" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="M78" s="1" t="s">
+      <c r="N78" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="N78" s="1" t="s">
+      <c r="O78" s="1" t="s">
         <v>825</v>
-      </c>
-      <c r="O78" s="1" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="79" spans="1:15">
       <c r="A79" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="B79" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>827</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="D79" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="E79" s="2">
+        <v>0</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>828</v>
       </c>
-      <c r="D79" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="E79" s="2">
-        <v>0</v>
-      </c>
-      <c r="F79" s="1" t="s">
+      <c r="G79" s="1" t="s">
         <v>829</v>
       </c>
-      <c r="G79" s="1" t="s">
+      <c r="H79" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="H79" s="1" t="s">
+      <c r="I79" s="2">
+        <v>0</v>
+      </c>
+      <c r="J79" s="1" t="s">
         <v>831</v>
       </c>
-      <c r="I79" s="2">
-        <v>0</v>
-      </c>
-      <c r="J79" s="1" t="s">
+      <c r="K79" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="K79" s="1" t="s">
+      <c r="L79" s="1" t="s">
         <v>833</v>
       </c>
-      <c r="L79" s="1" t="s">
+      <c r="M79" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="M79" s="1" t="s">
+      <c r="N79" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="N79" s="1" t="s">
+      <c r="O79" s="1" t="s">
         <v>836</v>
-      </c>
-      <c r="O79" s="1" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="80" spans="1:15">
       <c r="A80" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="B80" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="D80" s="1" t="s">
         <v>839</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="E80" s="2">
+        <v>0</v>
+      </c>
+      <c r="F80" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="E80" s="2">
-        <v>0</v>
-      </c>
-      <c r="F80" s="1" t="s">
+      <c r="G80" s="1" t="s">
         <v>841</v>
       </c>
-      <c r="G80" s="1" t="s">
+      <c r="H80" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="I80" s="2">
+        <v>0</v>
+      </c>
+      <c r="J80" s="1" t="s">
         <v>842</v>
       </c>
-      <c r="H80" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="I80" s="2">
-        <v>0</v>
-      </c>
-      <c r="J80" s="1" t="s">
+      <c r="K80" s="1" t="s">
         <v>843</v>
       </c>
-      <c r="K80" s="1" t="s">
+      <c r="L80" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="L80" s="1" t="s">
+      <c r="M80" s="1" t="s">
         <v>845</v>
       </c>
-      <c r="M80" s="1" t="s">
+      <c r="N80" s="1" t="s">
         <v>846</v>
       </c>
-      <c r="N80" s="1" t="s">
+      <c r="O80" s="1" t="s">
         <v>847</v>
-      </c>
-      <c r="O80" s="1" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="81" spans="1:15">
       <c r="A81" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="B81" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="D81" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="E81" s="2">
+        <v>0</v>
+      </c>
+      <c r="F81" s="1" t="s">
         <v>851</v>
       </c>
-      <c r="E81" s="2">
-        <v>0</v>
-      </c>
-      <c r="F81" s="1" t="s">
+      <c r="G81" s="1" t="s">
         <v>852</v>
       </c>
-      <c r="G81" s="1" t="s">
+      <c r="H81" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="I81" s="2">
+        <v>0</v>
+      </c>
+      <c r="J81" s="1" t="s">
         <v>853</v>
       </c>
-      <c r="H81" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="I81" s="2">
-        <v>0</v>
-      </c>
-      <c r="J81" s="1" t="s">
+      <c r="K81" s="1" t="s">
         <v>854</v>
       </c>
-      <c r="K81" s="1" t="s">
+      <c r="L81" s="1" t="s">
         <v>855</v>
       </c>
-      <c r="L81" s="1" t="s">
+      <c r="M81" s="1" t="s">
         <v>856</v>
       </c>
-      <c r="M81" s="1" t="s">
+      <c r="N81" s="1" t="s">
         <v>857</v>
       </c>
-      <c r="N81" s="1" t="s">
+      <c r="O81" s="1" t="s">
         <v>858</v>
-      </c>
-      <c r="O81" s="1" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="82" spans="1:15">
       <c r="A82" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="B82" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>860</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="D82" s="1" t="s">
         <v>861</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="E82" s="2">
+        <v>0</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="E82" s="2">
-        <v>0</v>
-      </c>
-      <c r="F82" s="1" t="s">
+      <c r="G82" s="1" t="s">
         <v>863</v>
       </c>
-      <c r="G82" s="1" t="s">
+      <c r="H82" s="1" t="s">
         <v>864</v>
       </c>
-      <c r="H82" s="1" t="s">
+      <c r="I82" s="2">
+        <v>0</v>
+      </c>
+      <c r="J82" s="1" t="s">
         <v>865</v>
       </c>
-      <c r="I82" s="2">
-        <v>0</v>
-      </c>
-      <c r="J82" s="1" t="s">
+      <c r="K82" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="K82" s="1" t="s">
+      <c r="L82" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="M82" s="1" t="s">
         <v>867</v>
       </c>
-      <c r="L82" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="M82" s="1" t="s">
+      <c r="N82" s="1" t="s">
         <v>868</v>
       </c>
-      <c r="N82" s="1" t="s">
+      <c r="O82" s="1" t="s">
         <v>869</v>
-      </c>
-      <c r="O82" s="1" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="83" spans="1:15">
       <c r="A83" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="B83" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>871</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="D83" s="1" t="s">
         <v>872</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="E83" s="2">
+        <v>0</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="E83" s="2">
-        <v>0</v>
-      </c>
-      <c r="F83" s="1" t="s">
+      <c r="G83" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="H83" s="1" t="s">
         <v>874</v>
       </c>
-      <c r="G83" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="H83" s="1" t="s">
+      <c r="I83" s="2">
+        <v>0</v>
+      </c>
+      <c r="J83" s="1" t="s">
         <v>875</v>
       </c>
-      <c r="I83" s="2">
-        <v>0</v>
-      </c>
-      <c r="J83" s="1" t="s">
+      <c r="K83" s="1" t="s">
         <v>876</v>
       </c>
-      <c r="K83" s="1" t="s">
+      <c r="L83" s="1" t="s">
         <v>877</v>
       </c>
-      <c r="L83" s="1" t="s">
+      <c r="M83" s="1" t="s">
         <v>878</v>
       </c>
-      <c r="M83" s="1" t="s">
+      <c r="N83" s="1" t="s">
         <v>879</v>
       </c>
-      <c r="N83" s="1" t="s">
+      <c r="O83" s="1" t="s">
         <v>880</v>
-      </c>
-      <c r="O83" s="1" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="84" spans="1:15">
       <c r="A84" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="B84" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>882</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="D84" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="E84" s="2">
+        <v>0</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>884</v>
       </c>
-      <c r="E84" s="2">
-        <v>0</v>
-      </c>
-      <c r="F84" s="1" t="s">
+      <c r="G84" s="1" t="s">
         <v>885</v>
       </c>
-      <c r="G84" s="1" t="s">
+      <c r="H84" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="H84" s="1" t="s">
+      <c r="I84" s="2">
+        <v>0</v>
+      </c>
+      <c r="J84" s="1" t="s">
         <v>887</v>
       </c>
-      <c r="I84" s="2">
-        <v>0</v>
-      </c>
-      <c r="J84" s="1" t="s">
+      <c r="K84" s="1" t="s">
         <v>888</v>
       </c>
-      <c r="K84" s="1" t="s">
+      <c r="L84" s="1" t="s">
         <v>889</v>
       </c>
-      <c r="L84" s="1" t="s">
+      <c r="M84" s="1" t="s">
         <v>890</v>
       </c>
-      <c r="M84" s="1" t="s">
+      <c r="N84" s="1" t="s">
         <v>891</v>
       </c>
-      <c r="N84" s="1" t="s">
+      <c r="O84" s="1" t="s">
         <v>892</v>
-      </c>
-      <c r="O84" s="1" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="85" spans="1:15">
       <c r="A85" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="B85" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>894</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="D85" s="1" t="s">
         <v>895</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="E85" s="2">
+        <v>0</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>896</v>
       </c>
-      <c r="E85" s="2">
-        <v>0</v>
-      </c>
-      <c r="F85" s="1" t="s">
+      <c r="G85" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="G85" s="1" t="s">
+      <c r="H85" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="H85" s="1" t="s">
+      <c r="I85" s="2">
+        <v>0</v>
+      </c>
+      <c r="J85" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="I85" s="2">
-        <v>0</v>
-      </c>
-      <c r="J85" s="1" t="s">
+      <c r="K85" s="1" t="s">
         <v>900</v>
       </c>
-      <c r="K85" s="1" t="s">
+      <c r="L85" s="1" t="s">
         <v>901</v>
       </c>
-      <c r="L85" s="1" t="s">
+      <c r="M85" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="M85" s="1" t="s">
+      <c r="N85" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="N85" s="1" t="s">
+      <c r="O85" s="1" t="s">
         <v>904</v>
-      </c>
-      <c r="O85" s="1" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="86" spans="1:15">
       <c r="A86" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B86" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>906</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="D86" s="1" t="s">
         <v>907</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="E86" s="2">
+        <v>0</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>908</v>
       </c>
-      <c r="E86" s="2">
-        <v>0</v>
-      </c>
-      <c r="F86" s="1" t="s">
+      <c r="G86" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="H86" s="1" t="s">
         <v>909</v>
       </c>
-      <c r="G86" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="H86" s="1" t="s">
+      <c r="I86" s="2">
+        <v>0</v>
+      </c>
+      <c r="J86" s="1" t="s">
         <v>910</v>
       </c>
-      <c r="I86" s="2">
-        <v>0</v>
-      </c>
-      <c r="J86" s="1" t="s">
+      <c r="K86" s="1" t="s">
         <v>911</v>
       </c>
-      <c r="K86" s="1" t="s">
+      <c r="L86" s="1" t="s">
         <v>912</v>
       </c>
-      <c r="L86" s="1" t="s">
+      <c r="M86" s="1" t="s">
         <v>913</v>
       </c>
-      <c r="M86" s="1" t="s">
+      <c r="N86" s="1" t="s">
         <v>914</v>
       </c>
-      <c r="N86" s="1" t="s">
+      <c r="O86" s="1" t="s">
         <v>915</v>
-      </c>
-      <c r="O86" s="1" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="87" spans="1:15">
       <c r="A87" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="B87" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>917</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="D87" s="1" t="s">
         <v>918</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="E87" s="2">
+        <v>0</v>
+      </c>
+      <c r="F87" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="E87" s="2">
-        <v>0</v>
-      </c>
-      <c r="F87" s="1" t="s">
+      <c r="G87" s="1" t="s">
         <v>920</v>
       </c>
-      <c r="G87" s="1" t="s">
+      <c r="H87" s="1" t="s">
         <v>921</v>
       </c>
-      <c r="H87" s="1" t="s">
+      <c r="I87" s="2">
+        <v>0</v>
+      </c>
+      <c r="J87" s="1" t="s">
         <v>922</v>
       </c>
-      <c r="I87" s="2">
-        <v>0</v>
-      </c>
-      <c r="J87" s="1" t="s">
+      <c r="K87" s="1" t="s">
         <v>923</v>
       </c>
-      <c r="K87" s="1" t="s">
+      <c r="L87" s="1" t="s">
         <v>924</v>
       </c>
-      <c r="L87" s="1" t="s">
+      <c r="M87" s="1" t="s">
         <v>925</v>
       </c>
-      <c r="M87" s="1" t="s">
+      <c r="N87" s="1" t="s">
         <v>926</v>
       </c>
-      <c r="N87" s="1" t="s">
+      <c r="O87" s="1" t="s">
         <v>927</v>
-      </c>
-      <c r="O87" s="1" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="88" spans="1:15">
       <c r="A88" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="B88" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="C88" s="1" t="s">
         <v>929</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="D88" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="E88" s="2">
+        <v>0</v>
+      </c>
+      <c r="F88" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="E88" s="2">
-        <v>0</v>
-      </c>
-      <c r="F88" s="1" t="s">
+      <c r="G88" s="1" t="s">
         <v>931</v>
       </c>
-      <c r="G88" s="1" t="s">
+      <c r="H88" s="1" t="s">
         <v>932</v>
       </c>
-      <c r="H88" s="1" t="s">
+      <c r="I88" s="2">
+        <v>0</v>
+      </c>
+      <c r="J88" s="1" t="s">
         <v>933</v>
       </c>
-      <c r="I88" s="2">
-        <v>0</v>
-      </c>
-      <c r="J88" s="1" t="s">
+      <c r="K88" s="1" t="s">
         <v>934</v>
       </c>
-      <c r="K88" s="1" t="s">
+      <c r="L88" s="1" t="s">
         <v>935</v>
       </c>
-      <c r="L88" s="1" t="s">
+      <c r="M88" s="1" t="s">
         <v>936</v>
       </c>
-      <c r="M88" s="1" t="s">
+      <c r="N88" s="1" t="s">
         <v>937</v>
       </c>
-      <c r="N88" s="1" t="s">
+      <c r="O88" s="1" t="s">
         <v>938</v>
-      </c>
-      <c r="O88" s="1" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="89" spans="1:15">
       <c r="A89" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="B89" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>940</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="D89" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="E89" s="2">
+        <v>0</v>
+      </c>
+      <c r="F89" s="1" t="s">
         <v>941</v>
       </c>
-      <c r="D89" s="1" t="s">
-        <v>919</v>
-      </c>
-      <c r="E89" s="2">
-        <v>0</v>
-      </c>
-      <c r="F89" s="1" t="s">
+      <c r="G89" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="H89" s="1" t="s">
         <v>942</v>
       </c>
-      <c r="G89" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="H89" s="1" t="s">
+      <c r="I89" s="2">
+        <v>0</v>
+      </c>
+      <c r="J89" s="1" t="s">
         <v>943</v>
       </c>
-      <c r="I89" s="2">
-        <v>0</v>
-      </c>
-      <c r="J89" s="1" t="s">
+      <c r="K89" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="L89" s="1" t="s">
         <v>944</v>
       </c>
-      <c r="K89" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="L89" s="1" t="s">
+      <c r="M89" s="1" t="s">
         <v>945</v>
       </c>
-      <c r="M89" s="1" t="s">
+      <c r="N89" s="1" t="s">
         <v>946</v>
       </c>
-      <c r="N89" s="1" t="s">
+      <c r="O89" s="1" t="s">
         <v>947</v>
-      </c>
-      <c r="O89" s="1" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="90" spans="1:15">
       <c r="A90" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="B90" s="1" t="s">
+        <v>948</v>
+      </c>
+      <c r="C90" s="1" t="s">
         <v>949</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="D90" s="1" t="s">
         <v>950</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="E90" s="2">
+        <v>0</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="E90" s="2">
-        <v>0</v>
-      </c>
-      <c r="F90" s="1" t="s">
+      <c r="G90" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="G90" s="1" t="s">
+      <c r="H90" s="1" t="s">
         <v>953</v>
       </c>
-      <c r="H90" s="1" t="s">
+      <c r="I90" s="2">
+        <v>0</v>
+      </c>
+      <c r="J90" s="1" t="s">
         <v>954</v>
       </c>
-      <c r="I90" s="2">
-        <v>0</v>
-      </c>
-      <c r="J90" s="1" t="s">
+      <c r="K90" s="1" t="s">
         <v>955</v>
       </c>
-      <c r="K90" s="1" t="s">
+      <c r="L90" s="1" t="s">
         <v>956</v>
       </c>
-      <c r="L90" s="1" t="s">
+      <c r="M90" s="1" t="s">
         <v>957</v>
       </c>
-      <c r="M90" s="1" t="s">
+      <c r="N90" s="1" t="s">
         <v>958</v>
       </c>
-      <c r="N90" s="1" t="s">
+      <c r="O90" s="1" t="s">
         <v>959</v>
-      </c>
-      <c r="O90" s="1" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="91" spans="1:15">
       <c r="A91" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="B91" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>961</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="D91" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="E91" s="2">
+        <v>0</v>
+      </c>
+      <c r="F91" s="1" t="s">
         <v>962</v>
       </c>
-      <c r="D91" s="1" t="s">
-        <v>808</v>
-      </c>
-      <c r="E91" s="2">
-        <v>0</v>
-      </c>
-      <c r="F91" s="1" t="s">
+      <c r="G91" s="1" t="s">
         <v>963</v>
       </c>
-      <c r="G91" s="1" t="s">
+      <c r="H91" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="I91" s="2">
+        <v>0</v>
+      </c>
+      <c r="J91" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="H91" s="1" t="s">
-        <v>887</v>
-      </c>
-      <c r="I91" s="2">
-        <v>0</v>
-      </c>
-      <c r="J91" s="1" t="s">
+      <c r="K91" s="1" t="s">
         <v>965</v>
       </c>
-      <c r="K91" s="1" t="s">
+      <c r="L91" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="M91" s="1" t="s">
         <v>966</v>
       </c>
-      <c r="L91" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="M91" s="1" t="s">
+      <c r="N91" s="1" t="s">
         <v>967</v>
       </c>
-      <c r="N91" s="1" t="s">
+      <c r="O91" s="1" t="s">
         <v>968</v>
-      </c>
-      <c r="O91" s="1" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="92" spans="1:15">
       <c r="A92" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="B92" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="C92" s="1" t="s">
         <v>970</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="D92" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="E92" s="2">
+        <v>0</v>
+      </c>
+      <c r="F92" s="1" t="s">
         <v>971</v>
       </c>
-      <c r="D92" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="E92" s="2">
-        <v>0</v>
-      </c>
-      <c r="F92" s="1" t="s">
+      <c r="G92" s="1" t="s">
         <v>972</v>
       </c>
-      <c r="G92" s="1" t="s">
+      <c r="H92" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="I92" s="2">
+        <v>0</v>
+      </c>
+      <c r="J92" s="1" t="s">
         <v>973</v>
       </c>
-      <c r="H92" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="I92" s="2">
-        <v>0</v>
-      </c>
-      <c r="J92" s="1" t="s">
+      <c r="K92" s="1" t="s">
         <v>974</v>
       </c>
-      <c r="K92" s="1" t="s">
+      <c r="L92" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="M92" s="1" t="s">
         <v>975</v>
       </c>
-      <c r="L92" s="1" t="s">
-        <v>913</v>
-      </c>
-      <c r="M92" s="1" t="s">
+      <c r="N92" s="1" t="s">
         <v>976</v>
       </c>
-      <c r="N92" s="1" t="s">
+      <c r="O92" s="1" t="s">
         <v>977</v>
-      </c>
-      <c r="O92" s="1" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="93" spans="1:15">
       <c r="A93" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="B93" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>979</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="D93" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="E93" s="2">
+        <v>0</v>
+      </c>
+      <c r="F93" s="1" t="s">
         <v>980</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>945</v>
-      </c>
-      <c r="E93" s="2">
-        <v>0</v>
-      </c>
-      <c r="F93" s="1" t="s">
+      <c r="G93" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="G93" s="1" t="s">
+      <c r="H93" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="I93" s="2">
+        <v>0</v>
+      </c>
+      <c r="J93" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="H93" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="I93" s="2">
-        <v>0</v>
-      </c>
-      <c r="J93" s="1" t="s">
+      <c r="K93" s="1" t="s">
         <v>983</v>
       </c>
-      <c r="K93" s="1" t="s">
+      <c r="L93" s="1" t="s">
         <v>984</v>
       </c>
-      <c r="L93" s="1" t="s">
+      <c r="M93" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="M93" s="1" t="s">
+      <c r="N93" s="1" t="s">
         <v>986</v>
       </c>
-      <c r="N93" s="1" t="s">
+      <c r="O93" s="1" t="s">
         <v>987</v>
-      </c>
-      <c r="O93" s="1" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="94" spans="1:15">
       <c r="A94" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="B94" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>989</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="D94" s="1" t="s">
         <v>990</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="E94" s="2">
+        <v>0</v>
+      </c>
+      <c r="F94" s="1" t="s">
         <v>991</v>
       </c>
-      <c r="E94" s="2">
-        <v>0</v>
-      </c>
-      <c r="F94" s="1" t="s">
+      <c r="G94" s="1" t="s">
         <v>992</v>
       </c>
-      <c r="G94" s="1" t="s">
+      <c r="H94" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="H94" s="1" t="s">
+      <c r="I94" s="2">
+        <v>0</v>
+      </c>
+      <c r="J94" s="1" t="s">
         <v>994</v>
       </c>
-      <c r="I94" s="2">
-        <v>0</v>
-      </c>
-      <c r="J94" s="1" t="s">
+      <c r="K94" s="1" t="s">
         <v>995</v>
       </c>
-      <c r="K94" s="1" t="s">
+      <c r="L94" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="L94" s="1" t="s">
+      <c r="M94" s="1" t="s">
         <v>997</v>
       </c>
-      <c r="M94" s="1" t="s">
+      <c r="N94" s="1" t="s">
         <v>998</v>
       </c>
-      <c r="N94" s="1" t="s">
+      <c r="O94" s="1" t="s">
         <v>999</v>
-      </c>
-      <c r="O94" s="1" t="s">
-        <v>1000</v>
       </c>
     </row>
     <row r="95" spans="1:15">
       <c r="A95" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="B95" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>1001</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="D95" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E95" s="2">
+        <v>0</v>
+      </c>
+      <c r="F95" s="1" t="s">
         <v>1002</v>
       </c>
-      <c r="D95" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="E95" s="2">
-        <v>0</v>
-      </c>
-      <c r="F95" s="1" t="s">
+      <c r="G95" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="G95" s="1" t="s">
+      <c r="H95" s="1" t="s">
         <v>1004</v>
       </c>
-      <c r="H95" s="1" t="s">
+      <c r="I95" s="2">
+        <v>0</v>
+      </c>
+      <c r="J95" s="1" t="s">
         <v>1005</v>
       </c>
-      <c r="I95" s="2">
-        <v>0</v>
-      </c>
-      <c r="J95" s="1" t="s">
+      <c r="K95" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="K95" s="1" t="s">
+      <c r="L95" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="L95" s="1" t="s">
+      <c r="M95" s="1" t="s">
         <v>1008</v>
       </c>
-      <c r="M95" s="1" t="s">
+      <c r="N95" s="1" t="s">
         <v>1009</v>
       </c>
-      <c r="N95" s="1" t="s">
+      <c r="O95" s="1" t="s">
         <v>1010</v>
-      </c>
-      <c r="O95" s="1" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="96" spans="1:15">
       <c r="A96" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="B96" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>1012</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="D96" s="1" t="s">
         <v>1013</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="E96" s="2">
+        <v>0</v>
+      </c>
+      <c r="F96" s="1" t="s">
         <v>1014</v>
       </c>
-      <c r="E96" s="2">
-        <v>0</v>
-      </c>
-      <c r="F96" s="1" t="s">
+      <c r="G96" s="1" t="s">
         <v>1015</v>
       </c>
-      <c r="G96" s="1" t="s">
+      <c r="H96" s="1" t="s">
         <v>1016</v>
       </c>
-      <c r="H96" s="1" t="s">
+      <c r="I96" s="2">
+        <v>0</v>
+      </c>
+      <c r="J96" s="1" t="s">
         <v>1017</v>
       </c>
-      <c r="I96" s="2">
-        <v>0</v>
-      </c>
-      <c r="J96" s="1" t="s">
+      <c r="K96" s="1" t="s">
         <v>1018</v>
       </c>
-      <c r="K96" s="1" t="s">
+      <c r="L96" s="1" t="s">
         <v>1019</v>
       </c>
-      <c r="L96" s="1" t="s">
+      <c r="M96" s="1" t="s">
         <v>1020</v>
       </c>
-      <c r="M96" s="1" t="s">
+      <c r="N96" s="1" t="s">
         <v>1021</v>
       </c>
-      <c r="N96" s="1" t="s">
+      <c r="O96" s="1" t="s">
         <v>1022</v>
-      </c>
-      <c r="O96" s="1" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="97" spans="1:15">
       <c r="A97" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="B97" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C97" s="1" t="s">
         <v>1024</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="D97" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="E97" s="2">
+        <v>0</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>1025</v>
       </c>
-      <c r="D97" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="E97" s="2">
-        <v>0</v>
-      </c>
-      <c r="F97" s="1" t="s">
+      <c r="G97" s="1" t="s">
         <v>1026</v>
       </c>
-      <c r="G97" s="1" t="s">
+      <c r="H97" s="1" t="s">
         <v>1027</v>
       </c>
-      <c r="H97" s="1" t="s">
+      <c r="I97" s="2">
+        <v>0</v>
+      </c>
+      <c r="J97" s="1" t="s">
         <v>1028</v>
       </c>
-      <c r="I97" s="2">
-        <v>0</v>
-      </c>
-      <c r="J97" s="1" t="s">
+      <c r="K97" s="1" t="s">
         <v>1029</v>
       </c>
-      <c r="K97" s="1" t="s">
+      <c r="L97" s="1" t="s">
         <v>1030</v>
       </c>
-      <c r="L97" s="1" t="s">
+      <c r="M97" s="1" t="s">
         <v>1031</v>
       </c>
-      <c r="M97" s="1" t="s">
+      <c r="N97" s="1" t="s">
         <v>1032</v>
       </c>
-      <c r="N97" s="1" t="s">
+      <c r="O97" s="1" t="s">
         <v>1033</v>
-      </c>
-      <c r="O97" s="1" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="98" spans="1:15">
       <c r="A98" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="B98" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C98" s="1" t="s">
         <v>1035</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="D98" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="E98" s="2">
+        <v>0</v>
+      </c>
+      <c r="F98" s="1" t="s">
         <v>1036</v>
       </c>
-      <c r="D98" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="E98" s="2">
-        <v>0</v>
-      </c>
-      <c r="F98" s="1" t="s">
+      <c r="G98" s="1" t="s">
         <v>1037</v>
       </c>
-      <c r="G98" s="1" t="s">
+      <c r="H98" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="I98" s="2">
+        <v>0</v>
+      </c>
+      <c r="J98" s="1" t="s">
         <v>1038</v>
       </c>
-      <c r="H98" s="1" t="s">
-        <v>692</v>
-      </c>
-      <c r="I98" s="2">
-        <v>0</v>
-      </c>
-      <c r="J98" s="1" t="s">
+      <c r="K98" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="L98" s="1" t="s">
         <v>1039</v>
       </c>
-      <c r="K98" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="L98" s="1" t="s">
+      <c r="M98" s="1" t="s">
         <v>1040</v>
       </c>
-      <c r="M98" s="1" t="s">
+      <c r="N98" s="1" t="s">
         <v>1041</v>
       </c>
-      <c r="N98" s="1" t="s">
+      <c r="O98" s="1" t="s">
         <v>1042</v>
-      </c>
-      <c r="O98" s="1" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="99" spans="1:15">
       <c r="A99" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B99" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C99" s="1" t="s">
         <v>1044</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="D99" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="E99" s="2">
+        <v>0</v>
+      </c>
+      <c r="F99" s="1" t="s">
         <v>1045</v>
       </c>
-      <c r="D99" s="1" t="s">
-        <v>919</v>
-      </c>
-      <c r="E99" s="2">
-        <v>0</v>
-      </c>
-      <c r="F99" s="1" t="s">
+      <c r="G99" s="1" t="s">
         <v>1046</v>
       </c>
-      <c r="G99" s="1" t="s">
+      <c r="H99" s="1" t="s">
         <v>1047</v>
       </c>
-      <c r="H99" s="1" t="s">
+      <c r="I99" s="2">
+        <v>0</v>
+      </c>
+      <c r="J99" s="1" t="s">
         <v>1048</v>
       </c>
-      <c r="I99" s="2">
-        <v>0</v>
-      </c>
-      <c r="J99" s="1" t="s">
+      <c r="K99" s="1" t="s">
         <v>1049</v>
       </c>
-      <c r="K99" s="1" t="s">
+      <c r="L99" s="1" t="s">
         <v>1050</v>
       </c>
-      <c r="L99" s="1" t="s">
+      <c r="M99" s="1" t="s">
         <v>1051</v>
       </c>
-      <c r="M99" s="1" t="s">
+      <c r="N99" s="1" t="s">
         <v>1052</v>
       </c>
-      <c r="N99" s="1" t="s">
+      <c r="O99" s="1" t="s">
         <v>1053</v>
-      </c>
-      <c r="O99" s="1" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="100" spans="1:15">
       <c r="A100" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="B100" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>1055</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="D100" s="1" t="s">
         <v>1056</v>
       </c>
-      <c r="D100" s="1" t="s">
+      <c r="E100" s="2">
+        <v>0</v>
+      </c>
+      <c r="F100" s="1" t="s">
         <v>1057</v>
       </c>
-      <c r="E100" s="2">
-        <v>0</v>
-      </c>
-      <c r="F100" s="1" t="s">
+      <c r="G100" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="H100" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="G100" s="1" t="s">
-        <v>889</v>
-      </c>
-      <c r="H100" s="1" t="s">
+      <c r="I100" s="2">
+        <v>0</v>
+      </c>
+      <c r="J100" s="1" t="s">
         <v>1059</v>
       </c>
-      <c r="I100" s="2">
-        <v>0</v>
-      </c>
-      <c r="J100" s="1" t="s">
+      <c r="K100" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="L100" s="1" t="s">
         <v>1060</v>
       </c>
-      <c r="K100" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="L100" s="1" t="s">
+      <c r="M100" s="1" t="s">
         <v>1061</v>
       </c>
-      <c r="M100" s="1" t="s">
+      <c r="N100" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="N100" s="1" t="s">
+      <c r="O100" s="1" t="s">
         <v>1063</v>
-      </c>
-      <c r="O100" s="1" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="101" spans="1:15">
       <c r="A101" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="B101" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C101" s="1" t="s">
         <v>1065</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="D101" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="E101" s="2">
+        <v>0</v>
+      </c>
+      <c r="F101" s="1" t="s">
         <v>1066</v>
       </c>
-      <c r="D101" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="E101" s="2">
-        <v>0</v>
-      </c>
-      <c r="F101" s="1" t="s">
+      <c r="G101" s="1" t="s">
         <v>1067</v>
       </c>
-      <c r="G101" s="1" t="s">
+      <c r="H101" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="I101" s="2">
+        <v>0</v>
+      </c>
+      <c r="J101" s="1" t="s">
         <v>1068</v>
       </c>
-      <c r="H101" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="I101" s="2">
-        <v>0</v>
-      </c>
-      <c r="J101" s="1" t="s">
+      <c r="K101" s="1" t="s">
         <v>1069</v>
       </c>
-      <c r="K101" s="1" t="s">
+      <c r="L101" s="1" t="s">
         <v>1070</v>
       </c>
-      <c r="L101" s="1" t="s">
+      <c r="M101" s="1" t="s">
         <v>1071</v>
       </c>
-      <c r="M101" s="1" t="s">
+      <c r="N101" s="1" t="s">
         <v>1072</v>
       </c>
-      <c r="N101" s="1" t="s">
+      <c r="O101" s="1" t="s">
         <v>1073</v>
-      </c>
-      <c r="O101" s="1" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="102" spans="1:15">
       <c r="A102" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="B102" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C102" s="1" t="s">
         <v>1075</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="D102" s="1" t="s">
         <v>1076</v>
       </c>
-      <c r="D102" s="1" t="s">
+      <c r="E102" s="2">
+        <v>0</v>
+      </c>
+      <c r="F102" s="1" t="s">
         <v>1077</v>
       </c>
-      <c r="E102" s="2">
-        <v>0</v>
-      </c>
-      <c r="F102" s="1" t="s">
+      <c r="G102" s="1" t="s">
         <v>1078</v>
       </c>
-      <c r="G102" s="1" t="s">
+      <c r="H102" s="1" t="s">
         <v>1079</v>
       </c>
-      <c r="H102" s="1" t="s">
+      <c r="I102" s="2">
+        <v>0</v>
+      </c>
+      <c r="J102" s="1" t="s">
         <v>1080</v>
       </c>
-      <c r="I102" s="2">
-        <v>0</v>
-      </c>
-      <c r="J102" s="1" t="s">
+      <c r="K102" s="1" t="s">
         <v>1081</v>
       </c>
-      <c r="K102" s="1" t="s">
+      <c r="L102" s="1" t="s">
         <v>1082</v>
       </c>
-      <c r="L102" s="1" t="s">
+      <c r="M102" s="1" t="s">
         <v>1083</v>
       </c>
-      <c r="M102" s="1" t="s">
+      <c r="N102" s="1" t="s">
         <v>1084</v>
       </c>
-      <c r="N102" s="1" t="s">
+      <c r="O102" s="1" t="s">
         <v>1085</v>
-      </c>
-      <c r="O102" s="1" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="103" spans="1:15">
       <c r="A103" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="B103" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>1087</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="D103" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="E103" s="2">
+        <v>0</v>
+      </c>
+      <c r="F103" s="1" t="s">
         <v>1088</v>
       </c>
-      <c r="D103" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="E103" s="2">
-        <v>0</v>
-      </c>
-      <c r="F103" s="1" t="s">
+      <c r="G103" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="H103" s="1" t="s">
         <v>1089</v>
       </c>
-      <c r="G103" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="H103" s="1" t="s">
+      <c r="I103" s="2">
+        <v>0</v>
+      </c>
+      <c r="J103" s="1" t="s">
         <v>1090</v>
       </c>
-      <c r="I103" s="2">
-        <v>0</v>
-      </c>
-      <c r="J103" s="1" t="s">
+      <c r="K103" s="1" t="s">
         <v>1091</v>
       </c>
-      <c r="K103" s="1" t="s">
+      <c r="L103" s="1" t="s">
         <v>1092</v>
       </c>
-      <c r="L103" s="1" t="s">
+      <c r="M103" s="1" t="s">
         <v>1093</v>
       </c>
-      <c r="M103" s="1" t="s">
+      <c r="N103" s="1" t="s">
         <v>1094</v>
       </c>
-      <c r="N103" s="1" t="s">
+      <c r="O103" s="1" t="s">
         <v>1095</v>
-      </c>
-      <c r="O103" s="1" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="104" spans="1:15">
       <c r="A104" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="B104" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>1097</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="D104" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="E104" s="2">
+        <v>0</v>
+      </c>
+      <c r="F104" s="1" t="s">
         <v>1098</v>
       </c>
-      <c r="D104" s="1" t="s">
-        <v>737</v>
-      </c>
-      <c r="E104" s="2">
-        <v>0</v>
-      </c>
-      <c r="F104" s="1" t="s">
+      <c r="G104" s="1" t="s">
         <v>1099</v>
       </c>
-      <c r="G104" s="1" t="s">
+      <c r="H104" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="I104" s="2">
+        <v>0</v>
+      </c>
+      <c r="J104" s="1" t="s">
         <v>1100</v>
       </c>
-      <c r="H104" s="1" t="s">
-        <v>887</v>
-      </c>
-      <c r="I104" s="2">
-        <v>0</v>
-      </c>
-      <c r="J104" s="1" t="s">
+      <c r="K104" s="1" t="s">
         <v>1101</v>
       </c>
-      <c r="K104" s="1" t="s">
+      <c r="L104" s="1" t="s">
         <v>1102</v>
       </c>
-      <c r="L104" s="1" t="s">
+      <c r="M104" s="1" t="s">
         <v>1103</v>
       </c>
-      <c r="M104" s="1" t="s">
+      <c r="N104" s="1" t="s">
         <v>1104</v>
       </c>
-      <c r="N104" s="1" t="s">
+      <c r="O104" s="1" t="s">
         <v>1105</v>
-      </c>
-      <c r="O104" s="1" t="s">
-        <v>1106</v>
       </c>
     </row>
     <row r="105" spans="1:15">
       <c r="A105" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="B105" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>1107</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="D105" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E105" s="2">
+        <v>0</v>
+      </c>
+      <c r="F105" s="1" t="s">
         <v>1108</v>
       </c>
-      <c r="D105" s="1" t="s">
-        <v>1077</v>
-      </c>
-      <c r="E105" s="2">
-        <v>0</v>
-      </c>
-      <c r="F105" s="1" t="s">
+      <c r="G105" s="1" t="s">
         <v>1109</v>
       </c>
-      <c r="G105" s="1" t="s">
+      <c r="H105" s="1" t="s">
         <v>1110</v>
       </c>
-      <c r="H105" s="1" t="s">
+      <c r="I105" s="2">
+        <v>0</v>
+      </c>
+      <c r="J105" s="1" t="s">
         <v>1111</v>
       </c>
-      <c r="I105" s="2">
-        <v>0</v>
-      </c>
-      <c r="J105" s="1" t="s">
+      <c r="K105" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="L105" s="1" t="s">
         <v>1112</v>
       </c>
-      <c r="K105" s="1" t="s">
-        <v>984</v>
-      </c>
-      <c r="L105" s="1" t="s">
+      <c r="M105" s="1" t="s">
         <v>1113</v>
       </c>
-      <c r="M105" s="1" t="s">
+      <c r="N105" s="1" t="s">
         <v>1114</v>
       </c>
-      <c r="N105" s="1" t="s">
+      <c r="O105" s="1" t="s">
         <v>1115</v>
-      </c>
-      <c r="O105" s="1" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="106" spans="1:15">
       <c r="A106" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="B106" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C106" s="1" t="s">
         <v>1117</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="D106" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="E106" s="2">
+        <v>0</v>
+      </c>
+      <c r="F106" s="1" t="s">
         <v>1118</v>
       </c>
-      <c r="D106" s="1" t="s">
-        <v>919</v>
-      </c>
-      <c r="E106" s="2">
-        <v>0</v>
-      </c>
-      <c r="F106" s="1" t="s">
+      <c r="G106" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="H106" s="1" t="s">
         <v>1119</v>
       </c>
-      <c r="G106" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="H106" s="1" t="s">
+      <c r="I106" s="2">
+        <v>0</v>
+      </c>
+      <c r="J106" s="1" t="s">
         <v>1120</v>
       </c>
-      <c r="I106" s="2">
-        <v>0</v>
-      </c>
-      <c r="J106" s="1" t="s">
+      <c r="K106" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="L106" s="1" t="s">
         <v>1121</v>
       </c>
-      <c r="K106" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="L106" s="1" t="s">
+      <c r="M106" s="1" t="s">
         <v>1122</v>
       </c>
-      <c r="M106" s="1" t="s">
+      <c r="N106" s="1" t="s">
         <v>1123</v>
       </c>
-      <c r="N106" s="1" t="s">
+      <c r="O106" s="1" t="s">
         <v>1124</v>
-      </c>
-      <c r="O106" s="1" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="107" spans="1:15">
       <c r="A107" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="B107" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C107" s="1" t="s">
         <v>1126</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="D107" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="E107" s="2">
+        <v>0</v>
+      </c>
+      <c r="F107" s="1" t="s">
         <v>1127</v>
       </c>
-      <c r="D107" s="1" t="s">
-        <v>808</v>
-      </c>
-      <c r="E107" s="2">
-        <v>0</v>
-      </c>
-      <c r="F107" s="1" t="s">
+      <c r="G107" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="G107" s="1" t="s">
+      <c r="H107" s="1" t="s">
         <v>1129</v>
       </c>
-      <c r="H107" s="1" t="s">
+      <c r="I107" s="2">
+        <v>0</v>
+      </c>
+      <c r="J107" s="1" t="s">
         <v>1130</v>
       </c>
-      <c r="I107" s="2">
-        <v>0</v>
-      </c>
-      <c r="J107" s="1" t="s">
+      <c r="K107" s="1" t="s">
         <v>1131</v>
       </c>
-      <c r="K107" s="1" t="s">
+      <c r="L107" s="1" t="s">
         <v>1132</v>
       </c>
-      <c r="L107" s="1" t="s">
+      <c r="M107" s="1" t="s">
         <v>1133</v>
       </c>
-      <c r="M107" s="1" t="s">
+      <c r="N107" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="N107" s="1" t="s">
+      <c r="O107" s="1" t="s">
         <v>1135</v>
-      </c>
-      <c r="O107" s="1" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="108" spans="1:15">
       <c r="A108" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="B108" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="D108" s="1" t="s">
         <v>1138</v>
       </c>
-      <c r="D108" s="1" t="s">
+      <c r="E108" s="2">
+        <v>0</v>
+      </c>
+      <c r="F108" s="1" t="s">
         <v>1139</v>
       </c>
-      <c r="E108" s="2">
-        <v>0</v>
-      </c>
-      <c r="F108" s="1" t="s">
+      <c r="G108" s="1" t="s">
         <v>1140</v>
       </c>
-      <c r="G108" s="1" t="s">
+      <c r="H108" s="1" t="s">
         <v>1141</v>
       </c>
-      <c r="H108" s="1" t="s">
+      <c r="I108" s="2">
+        <v>0</v>
+      </c>
+      <c r="J108" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="I108" s="2">
-        <v>0</v>
-      </c>
-      <c r="J108" s="1" t="s">
+      <c r="K108" s="1" t="s">
         <v>1143</v>
       </c>
-      <c r="K108" s="1" t="s">
+      <c r="L108" s="1" t="s">
         <v>1144</v>
       </c>
-      <c r="L108" s="1" t="s">
+      <c r="M108" s="1" t="s">
         <v>1145</v>
       </c>
-      <c r="M108" s="1" t="s">
+      <c r="N108" s="1" t="s">
         <v>1146</v>
       </c>
-      <c r="N108" s="1" t="s">
+      <c r="O108" s="1" t="s">
         <v>1147</v>
-      </c>
-      <c r="O108" s="1" t="s">
-        <v>1148</v>
       </c>
     </row>
     <row r="109" spans="1:15">
       <c r="A109" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C109" s="1" t="s">
         <v>1149</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="D109" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="E109" s="2">
+        <v>0</v>
+      </c>
+      <c r="F109" s="1" t="s">
         <v>1150</v>
       </c>
-      <c r="D109" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="E109" s="2">
-        <v>0</v>
-      </c>
-      <c r="F109" s="1" t="s">
+      <c r="G109" s="1" t="s">
         <v>1151</v>
       </c>
-      <c r="G109" s="1" t="s">
+      <c r="H109" s="1" t="s">
         <v>1152</v>
       </c>
-      <c r="H109" s="1" t="s">
+      <c r="I109" s="2">
+        <v>0</v>
+      </c>
+      <c r="J109" s="1" t="s">
         <v>1153</v>
       </c>
-      <c r="I109" s="2">
-        <v>0</v>
-      </c>
-      <c r="J109" s="1" t="s">
+      <c r="K109" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="L109" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="M109" s="1" t="s">
         <v>1154</v>
       </c>
-      <c r="K109" s="1" t="s">
-        <v>1007</v>
-      </c>
-      <c r="L109" s="1" t="s">
-        <v>896</v>
-      </c>
-      <c r="M109" s="1" t="s">
+      <c r="N109" s="1" t="s">
         <v>1155</v>
       </c>
-      <c r="N109" s="1" t="s">
+      <c r="O109" s="1" t="s">
         <v>1156</v>
-      </c>
-      <c r="O109" s="1" t="s">
-        <v>1157</v>
       </c>
     </row>
     <row r="110" spans="1:15">
       <c r="A110" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="B110" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C110" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="D110" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="E110" s="2">
+        <v>0</v>
+      </c>
+      <c r="F110" s="1" t="s">
         <v>1159</v>
       </c>
-      <c r="D110" s="1" t="s">
-        <v>991</v>
-      </c>
-      <c r="E110" s="2">
-        <v>0</v>
-      </c>
-      <c r="F110" s="1" t="s">
+      <c r="G110" s="1" t="s">
         <v>1160</v>
       </c>
-      <c r="G110" s="1" t="s">
+      <c r="H110" s="1" t="s">
         <v>1161</v>
       </c>
-      <c r="H110" s="1" t="s">
+      <c r="I110" s="2">
+        <v>0</v>
+      </c>
+      <c r="J110" s="1" t="s">
         <v>1162</v>
       </c>
-      <c r="I110" s="2">
-        <v>0</v>
-      </c>
-      <c r="J110" s="1" t="s">
+      <c r="K110" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="L110" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="M110" s="1" t="s">
         <v>1163</v>
       </c>
-      <c r="K110" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="L110" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="M110" s="1" t="s">
+      <c r="N110" s="1" t="s">
         <v>1164</v>
       </c>
-      <c r="N110" s="1" t="s">
+      <c r="O110" s="1" t="s">
         <v>1165</v>
-      </c>
-      <c r="O110" s="1" t="s">
-        <v>1166</v>
       </c>
     </row>
     <row r="111" spans="1:15">
       <c r="A111" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="B111" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>1167</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="D111" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="E111" s="2">
+        <v>0</v>
+      </c>
+      <c r="F111" s="1" t="s">
         <v>1168</v>
       </c>
-      <c r="D111" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="E111" s="2">
-        <v>0</v>
-      </c>
-      <c r="F111" s="1" t="s">
+      <c r="G111" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="H111" s="1" t="s">
         <v>1169</v>
       </c>
-      <c r="G111" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="H111" s="1" t="s">
+      <c r="I111" s="2">
+        <v>0</v>
+      </c>
+      <c r="J111" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="I111" s="2">
-        <v>0</v>
-      </c>
-      <c r="J111" s="1" t="s">
+      <c r="K111" s="1" t="s">
         <v>1171</v>
       </c>
-      <c r="K111" s="1" t="s">
+      <c r="L111" s="1" t="s">
         <v>1172</v>
       </c>
-      <c r="L111" s="1" t="s">
+      <c r="M111" s="1" t="s">
         <v>1173</v>
       </c>
-      <c r="M111" s="1" t="s">
+      <c r="N111" s="1" t="s">
         <v>1174</v>
       </c>
-      <c r="N111" s="1" t="s">
+      <c r="O111" s="1" t="s">
         <v>1175</v>
-      </c>
-      <c r="O111" s="1" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="112" spans="1:15">
       <c r="A112" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="B112" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>1177</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="D112" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="E112" s="2">
+        <v>0</v>
+      </c>
+      <c r="F112" s="1" t="s">
         <v>1178</v>
       </c>
-      <c r="D112" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="E112" s="2">
-        <v>0</v>
-      </c>
-      <c r="F112" s="1" t="s">
+      <c r="G112" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="I112" s="2">
+        <v>0</v>
+      </c>
+      <c r="J112" s="1" t="s">
         <v>1179</v>
       </c>
-      <c r="G112" s="1" t="s">
-        <v>921</v>
-      </c>
-      <c r="H112" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="I112" s="2">
-        <v>0</v>
-      </c>
-      <c r="J112" s="1" t="s">
+      <c r="K112" s="1" t="s">
         <v>1180</v>
       </c>
-      <c r="K112" s="1" t="s">
+      <c r="L112" s="1" t="s">
         <v>1181</v>
       </c>
-      <c r="L112" s="1" t="s">
+      <c r="M112" s="1" t="s">
         <v>1182</v>
       </c>
-      <c r="M112" s="1" t="s">
+      <c r="N112" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="N112" s="1" t="s">
+      <c r="O112" s="1" t="s">
         <v>1184</v>
-      </c>
-      <c r="O112" s="1" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="113" spans="1:15">
       <c r="A113" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="B113" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C113" s="1" t="s">
         <v>1186</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="D113" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="E113" s="2">
+        <v>0</v>
+      </c>
+      <c r="F113" s="1" t="s">
         <v>1187</v>
       </c>
-      <c r="D113" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="E113" s="2">
-        <v>0</v>
-      </c>
-      <c r="F113" s="1" t="s">
+      <c r="G113" s="1" t="s">
         <v>1188</v>
       </c>
-      <c r="G113" s="1" t="s">
+      <c r="H113" s="1" t="s">
         <v>1189</v>
       </c>
-      <c r="H113" s="1" t="s">
+      <c r="I113" s="2">
+        <v>0</v>
+      </c>
+      <c r="J113" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="I113" s="2">
-        <v>0</v>
-      </c>
-      <c r="J113" s="1" t="s">
+      <c r="K113" s="1" t="s">
         <v>1191</v>
       </c>
-      <c r="K113" s="1" t="s">
+      <c r="L113" s="1" t="s">
         <v>1192</v>
       </c>
-      <c r="L113" s="1" t="s">
+      <c r="M113" s="1" t="s">
         <v>1193</v>
       </c>
-      <c r="M113" s="1" t="s">
+      <c r="N113" s="1" t="s">
         <v>1194</v>
       </c>
-      <c r="N113" s="1" t="s">
+      <c r="O113" s="1" t="s">
         <v>1195</v>
-      </c>
-      <c r="O113" s="1" t="s">
-        <v>1196</v>
       </c>
     </row>
     <row r="114" spans="1:15">
       <c r="A114" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="B114" s="1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C114" s="1" t="s">
         <v>1197</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="D114" s="1" t="s">
         <v>1198</v>
       </c>
-      <c r="D114" s="1" t="s">
+      <c r="E114" s="2">
+        <v>0</v>
+      </c>
+      <c r="F114" s="1" t="s">
         <v>1199</v>
       </c>
-      <c r="E114" s="2">
-        <v>0</v>
-      </c>
-      <c r="F114" s="1" t="s">
+      <c r="G114" s="1" t="s">
         <v>1200</v>
       </c>
-      <c r="G114" s="1" t="s">
+      <c r="H114" s="1" t="s">
         <v>1201</v>
       </c>
-      <c r="H114" s="1" t="s">
+      <c r="I114" s="2">
+        <v>0</v>
+      </c>
+      <c r="J114" s="1" t="s">
         <v>1202</v>
       </c>
-      <c r="I114" s="2">
-        <v>0</v>
-      </c>
-      <c r="J114" s="1" t="s">
+      <c r="K114" s="1" t="s">
         <v>1203</v>
       </c>
-      <c r="K114" s="1" t="s">
+      <c r="L114" s="1" t="s">
         <v>1204</v>
       </c>
-      <c r="L114" s="1" t="s">
+      <c r="M114" s="1" t="s">
         <v>1205</v>
       </c>
-      <c r="M114" s="1" t="s">
+      <c r="N114" s="1" t="s">
         <v>1206</v>
       </c>
-      <c r="N114" s="1" t="s">
+      <c r="O114" s="1" t="s">
         <v>1207</v>
-      </c>
-      <c r="O114" s="1" t="s">
-        <v>1208</v>
       </c>
     </row>
     <row r="115" spans="1:15">
       <c r="A115" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="B115" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C115" s="1" t="s">
         <v>1209</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="D115" s="1" t="s">
         <v>1210</v>
       </c>
-      <c r="D115" s="1" t="s">
+      <c r="E115" s="2">
+        <v>0</v>
+      </c>
+      <c r="F115" s="1" t="s">
         <v>1211</v>
       </c>
-      <c r="E115" s="2">
-        <v>0</v>
-      </c>
-      <c r="F115" s="1" t="s">
+      <c r="G115" s="1" t="s">
         <v>1212</v>
       </c>
-      <c r="G115" s="1" t="s">
+      <c r="H115" s="1" t="s">
         <v>1213</v>
       </c>
-      <c r="H115" s="1" t="s">
+      <c r="I115" s="2">
+        <v>0</v>
+      </c>
+      <c r="J115" s="1" t="s">
         <v>1214</v>
       </c>
-      <c r="I115" s="2">
-        <v>0</v>
-      </c>
-      <c r="J115" s="1" t="s">
+      <c r="K115" s="1" t="s">
         <v>1215</v>
       </c>
-      <c r="K115" s="1" t="s">
+      <c r="L115" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="M115" s="1" t="s">
         <v>1216</v>
       </c>
-      <c r="L115" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="M115" s="1" t="s">
+      <c r="N115" s="1" t="s">
         <v>1217</v>
       </c>
-      <c r="N115" s="1" t="s">
+      <c r="O115" s="1" t="s">
         <v>1218</v>
-      </c>
-      <c r="O115" s="1" t="s">
-        <v>1219</v>
       </c>
     </row>
     <row r="116" spans="1:15">
       <c r="A116" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="B116" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>1220</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="D116" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="E116" s="2">
+        <v>0</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="G116" s="1" t="s">
         <v>1221</v>
       </c>
-      <c r="D116" s="1" t="s">
-        <v>957</v>
-      </c>
-      <c r="E116" s="2">
-        <v>0</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>897</v>
-      </c>
-      <c r="G116" s="1" t="s">
+      <c r="H116" s="1" t="s">
         <v>1222</v>
       </c>
-      <c r="H116" s="1" t="s">
+      <c r="I116" s="2">
+        <v>0</v>
+      </c>
+      <c r="J116" s="1" t="s">
         <v>1223</v>
       </c>
-      <c r="I116" s="2">
-        <v>0</v>
-      </c>
-      <c r="J116" s="1" t="s">
+      <c r="K116" s="1" t="s">
         <v>1224</v>
       </c>
-      <c r="K116" s="1" t="s">
+      <c r="L116" s="1" t="s">
         <v>1225</v>
       </c>
-      <c r="L116" s="1" t="s">
+      <c r="M116" s="1" t="s">
         <v>1226</v>
       </c>
-      <c r="M116" s="1" t="s">
+      <c r="N116" s="1" t="s">
         <v>1227</v>
       </c>
-      <c r="N116" s="1" t="s">
+      <c r="O116" s="1" t="s">
         <v>1228</v>
-      </c>
-      <c r="O116" s="1" t="s">
-        <v>1229</v>
       </c>
     </row>
     <row r="117" spans="1:15">
       <c r="A117" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="B117" s="1" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C117" s="1" t="s">
         <v>1230</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="D117" s="1" t="s">
         <v>1231</v>
       </c>
-      <c r="D117" s="1" t="s">
+      <c r="E117" s="2">
+        <v>0</v>
+      </c>
+      <c r="F117" s="1" t="s">
         <v>1232</v>
       </c>
-      <c r="E117" s="2">
-        <v>0</v>
-      </c>
-      <c r="F117" s="1" t="s">
+      <c r="G117" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="H117" s="1" t="s">
         <v>1233</v>
       </c>
-      <c r="G117" s="1" t="s">
-        <v>751</v>
-      </c>
-      <c r="H117" s="1" t="s">
+      <c r="I117" s="2">
+        <v>0</v>
+      </c>
+      <c r="J117" s="1" t="s">
         <v>1234</v>
       </c>
-      <c r="I117" s="2">
-        <v>0</v>
-      </c>
-      <c r="J117" s="1" t="s">
+      <c r="K117" s="1" t="s">
+        <v>1171</v>
+      </c>
+      <c r="L117" s="1" t="s">
         <v>1235</v>
       </c>
-      <c r="K117" s="1" t="s">
-        <v>1172</v>
-      </c>
-      <c r="L117" s="1" t="s">
+      <c r="M117" s="1" t="s">
         <v>1236</v>
       </c>
-      <c r="M117" s="1" t="s">
+      <c r="N117" s="1" t="s">
         <v>1237</v>
       </c>
-      <c r="N117" s="1" t="s">
+      <c r="O117" s="1" t="s">
         <v>1238</v>
-      </c>
-      <c r="O117" s="1" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="118" spans="1:15">
       <c r="A118" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="B118" s="1" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C118" s="1" t="s">
         <v>1240</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="D118" s="1" t="s">
         <v>1241</v>
       </c>
-      <c r="D118" s="1" t="s">
+      <c r="E118" s="2">
+        <v>0</v>
+      </c>
+      <c r="F118" s="1" t="s">
         <v>1242</v>
       </c>
-      <c r="E118" s="2">
-        <v>0</v>
-      </c>
-      <c r="F118" s="1" t="s">
+      <c r="G118" s="1" t="s">
         <v>1243</v>
       </c>
-      <c r="G118" s="1" t="s">
+      <c r="H118" s="1" t="s">
         <v>1244</v>
       </c>
-      <c r="H118" s="1" t="s">
+      <c r="I118" s="2">
+        <v>0</v>
+      </c>
+      <c r="J118" s="1" t="s">
         <v>1245</v>
       </c>
-      <c r="I118" s="2">
-        <v>0</v>
-      </c>
-      <c r="J118" s="1" t="s">
+      <c r="K118" s="1" t="s">
         <v>1246</v>
       </c>
-      <c r="K118" s="1" t="s">
+      <c r="L118" s="1" t="s">
         <v>1247</v>
       </c>
-      <c r="L118" s="1" t="s">
+      <c r="M118" s="1" t="s">
         <v>1248</v>
       </c>
-      <c r="M118" s="1" t="s">
+      <c r="N118" s="1" t="s">
         <v>1249</v>
       </c>
-      <c r="N118" s="1" t="s">
+      <c r="O118" s="1" t="s">
         <v>1250</v>
-      </c>
-      <c r="O118" s="1" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="119" spans="1:15">
       <c r="A119" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="B119" s="1" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>1252</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="D119" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="E119" s="2">
+        <v>0</v>
+      </c>
+      <c r="F119" s="1" t="s">
         <v>1253</v>
       </c>
-      <c r="D119" s="1" t="s">
-        <v>851</v>
-      </c>
-      <c r="E119" s="2">
-        <v>0</v>
-      </c>
-      <c r="F119" s="1" t="s">
+      <c r="G119" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="H119" s="1" t="s">
         <v>1254</v>
       </c>
-      <c r="G119" s="1" t="s">
-        <v>694</v>
-      </c>
-      <c r="H119" s="1" t="s">
+      <c r="I119" s="2">
+        <v>0</v>
+      </c>
+      <c r="J119" s="1" t="s">
         <v>1255</v>
       </c>
-      <c r="I119" s="2">
-        <v>0</v>
-      </c>
-      <c r="J119" s="1" t="s">
+      <c r="K119" s="1" t="s">
         <v>1256</v>
       </c>
-      <c r="K119" s="1" t="s">
+      <c r="L119" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="M119" s="1" t="s">
         <v>1257</v>
       </c>
-      <c r="L119" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="M119" s="1" t="s">
+      <c r="N119" s="1" t="s">
         <v>1258</v>
       </c>
-      <c r="N119" s="1" t="s">
+      <c r="O119" s="1" t="s">
         <v>1259</v>
-      </c>
-      <c r="O119" s="1" t="s">
-        <v>1260</v>
       </c>
     </row>
     <row r="120" spans="1:15">
       <c r="A120" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="B120" s="1" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C120" s="1" t="s">
         <v>1261</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="D120" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="E120" s="2">
+        <v>0</v>
+      </c>
+      <c r="F120" s="1" t="s">
         <v>1262</v>
       </c>
-      <c r="D120" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="E120" s="2">
-        <v>0</v>
-      </c>
-      <c r="F120" s="1" t="s">
+      <c r="G120" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="G120" s="1" t="s">
+      <c r="H120" s="1" t="s">
         <v>1264</v>
       </c>
-      <c r="H120" s="1" t="s">
+      <c r="I120" s="2">
+        <v>0</v>
+      </c>
+      <c r="J120" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I120" s="2">
-        <v>0</v>
-      </c>
-      <c r="J120" s="1" t="s">
+      <c r="K120" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="K120" s="1" t="s">
+      <c r="L120" s="1" t="s">
         <v>1267</v>
       </c>
-      <c r="L120" s="1" t="s">
+      <c r="M120" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="M120" s="1" t="s">
+      <c r="N120" s="1" t="s">
         <v>1269</v>
       </c>
-      <c r="N120" s="1" t="s">
+      <c r="O120" s="1" t="s">
         <v>1270</v>
-      </c>
-      <c r="O120" s="1" t="s">
-        <v>1271</v>
       </c>
     </row>
     <row r="121" spans="1:15">
       <c r="A121" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="B121" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C121" s="1" t="s">
         <v>1272</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="D121" s="1" t="s">
         <v>1273</v>
       </c>
-      <c r="D121" s="1" t="s">
+      <c r="E121" s="2">
+        <v>0</v>
+      </c>
+      <c r="F121" s="1" t="s">
         <v>1274</v>
       </c>
-      <c r="E121" s="2">
-        <v>0</v>
-      </c>
-      <c r="F121" s="1" t="s">
+      <c r="G121" s="1" t="s">
         <v>1275</v>
       </c>
-      <c r="G121" s="1" t="s">
+      <c r="H121" s="1" t="s">
         <v>1276</v>
       </c>
-      <c r="H121" s="1" t="s">
+      <c r="I121" s="2">
+        <v>0</v>
+      </c>
+      <c r="J121" s="1" t="s">
         <v>1277</v>
       </c>
-      <c r="I121" s="2">
-        <v>0</v>
-      </c>
-      <c r="J121" s="1" t="s">
+      <c r="K121" s="1" t="s">
         <v>1278</v>
       </c>
-      <c r="K121" s="1" t="s">
+      <c r="L121" s="1" t="s">
         <v>1279</v>
       </c>
-      <c r="L121" s="1" t="s">
+      <c r="M121" s="1" t="s">
         <v>1280</v>
       </c>
-      <c r="M121" s="1" t="s">
+      <c r="N121" s="1" t="s">
         <v>1281</v>
       </c>
-      <c r="N121" s="1" t="s">
+      <c r="O121" s="1" t="s">
         <v>1282</v>
-      </c>
-      <c r="O121" s="1" t="s">
-        <v>1283</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>